--- a/Frontend_Development_Practice_Bank.xlsx
+++ b/Frontend_Development_Practice_Bank.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q001-portfolio-hero-blueprint-html-beginner-challenge-001.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q001-portfolio-hero-blueprint-html-beginner-challenge-001.html</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q002-campus-club-home-structure-html-beginner-challenge-002.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q002-campus-club-home-structure-html-beginner-challenge-002.html</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q003-startup-about-storyline-html-beginner-challenge-003.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q003-startup-about-storyline-html-beginner-challenge-003.html</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q004-travel-blog-intro-layout-html-beginner-challenge-004.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q004-travel-blog-intro-layout-html-beginner-challenge-004.html</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q005-food-menu-showcase-page-html-beginner-challenge-005.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q005-food-menu-showcase-page-html-beginner-challenge-005.html</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q006-course-finder-landing-outline-html-beginner-challenge-006.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q006-course-finder-landing-outline-html-beginner-challenge-006.html</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q007-ngo-mission-page-structure-html-beginner-challenge-007.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q007-ngo-mission-page-structure-html-beginner-challenge-007.html</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q008-podcast-episode-landing-html-beginner-challenge-008.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q008-podcast-episode-landing-html-beginner-challenge-008.html</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q009-fitness-coach-intro-page-html-beginner-challenge-009.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q009-fitness-coach-intro-page-html-beginner-challenge-009.html</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q010-bookstore-discover-page-html-beginner-challenge-010.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q010-bookstore-discover-page-html-beginner-challenge-010.html</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q011-event-countdown-content-page-html-beginner-challenge-011.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q011-event-countdown-content-page-html-beginner-challenge-011.html</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q012-freelancer-service-page-skeleton-html-beginner-challenge-012.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q012-freelancer-service-page-skeleton-html-beginner-challenge-012.html</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q013-museum-exhibit-intro-page-html-beginner-challenge-013.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q013-museum-exhibit-intro-page-html-beginner-challenge-013.html</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q014-career-fair-info-page-html-beginner-challenge-014.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q014-career-fair-info-page-html-beginner-challenge-014.html</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q015-tech-meetup-announcement-page-html-beginner-challenge-015.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q015-tech-meetup-announcement-page-html-beginner-challenge-015.html</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q016-local-news-digest-home-html-beginner-challenge-016.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q016-local-news-digest-home-html-beginner-challenge-016.html</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q017-recipe-discovery-landing-html-beginner-challenge-017.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q017-recipe-discovery-landing-html-beginner-challenge-017.html</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q018-product-launch-intro-page-html-beginner-challenge-018.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q018-product-launch-intro-page-html-beginner-challenge-018.html</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q019-student-project-gallery-page-html-beginner-challenge-019.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q019-student-project-gallery-page-html-beginner-challenge-019.html</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q020-volunteer-drive-landing-html-beginner-challenge-020.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q020-volunteer-drive-landing-html-beginner-challenge-020.html</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q021-language-learning-home-html-beginner-challenge-021.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q021-language-learning-home-html-beginner-challenge-021.html</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q022-internship-portal-intro-html-beginner-challenge-022.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q022-internship-portal-intro-html-beginner-challenge-022.html</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q023-healthcare-awareness-page-html-beginner-challenge-023.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q023-healthcare-awareness-page-html-beginner-challenge-023.html</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q024-photography-journey-page-html-beginner-challenge-024.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q024-photography-journey-page-html-beginner-challenge-024.html</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q025-coding-bootcamp-info-page-html-beginner-challenge-025.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q025-coding-bootcamp-info-page-html-beginner-challenge-025.html</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q026-town-hall-notice-page-html-beginner-challenge-026.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q026-town-hall-notice-page-html-beginner-challenge-026.html</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q027-scholarship-program-intro-html-beginner-challenge-027.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q027-scholarship-program-intro-html-beginner-challenge-027.html</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q028-music-festival-welcome-page-html-beginner-challenge-028.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q028-music-festival-welcome-page-html-beginner-challenge-028.html</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q029-real-estate-listing-intro-html-beginner-challenge-029.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q029-real-estate-listing-intro-html-beginner-challenge-029.html</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/html/q030-climate-action-campaign-page-html-beginner-challenge-030.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/html/q030-climate-action-campaign-page-html-beginner-challenge-030.html</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q031-accessible-editorial-article-semantic-html-beginner-challenge-031.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q031-accessible-editorial-article-semantic-html-beginner-challenge-031.html</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q032-landmark-rich-government-notice-semantic-html-beginner-challenge-032.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q032-landmark-rich-government-notice-semantic-html-beginner-challenge-032.html</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q033-research-summary-with-sections-semantic-html-beginner-challenge-033.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q033-research-summary-with-sections-semantic-html-beginner-challenge-033.html</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q034-open-source-release-notes-semantic-html-beginner-challenge-034.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q034-open-source-release-notes-semantic-html-beginner-challenge-034.html</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q035-health-advisory-bulletin-semantic-html-beginner-challenge-035.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q035-health-advisory-bulletin-semantic-html-beginner-challenge-035.html</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q036-newsroom-feature-with-asides-semantic-html-beginner-challenge-036.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q036-newsroom-feature-with-asides-semantic-html-beginner-challenge-036.html</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q037-education-policy-explainer-semantic-html-beginner-challenge-037.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q037-education-policy-explainer-semantic-html-beginner-challenge-037.html</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q038-product-case-study-narrative-semantic-html-beginner-challenge-038.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q038-product-case-study-narrative-semantic-html-beginner-challenge-038.html</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q039-conference-report-with-time-data-semantic-html-beginner-challenge-039.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q039-conference-report-with-time-data-semantic-html-beginner-challenge-039.html</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q040-community-program-digest-semantic-html-beginner-challenge-040.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q040-community-program-digest-semantic-html-beginner-challenge-040.html</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q041-public-service-announcement-semantic-html-beginner-challenge-041.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q041-public-service-announcement-semantic-html-beginner-challenge-041.html</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q042-digital-magazine-story-flow-semantic-html-beginner-challenge-042.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q042-digital-magazine-story-flow-semantic-html-beginner-challenge-042.html</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q043-cinema-review-with-metadata-semantic-html-beginner-challenge-043.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q043-cinema-review-with-metadata-semantic-html-beginner-challenge-043.html</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q044-travel-guide-with-highlights-semantic-html-beginner-challenge-044.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q044-travel-guide-with-highlights-semantic-html-beginner-challenge-044.html</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q045-charity-report-with-figures-semantic-html-beginner-challenge-045.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q045-charity-report-with-figures-semantic-html-beginner-challenge-045.html</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q046-startup-milestone-chronicle-semantic-html-beginner-challenge-046.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q046-startup-milestone-chronicle-semantic-html-beginner-challenge-046.html</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q047-interview-transcript-publication-semantic-html-beginner-challenge-047.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q047-interview-transcript-publication-semantic-html-beginner-challenge-047.html</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q048-workshop-recap-article-semantic-html-beginner-challenge-048.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q048-workshop-recap-article-semantic-html-beginner-challenge-048.html</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q049-museum-research-abstract-semantic-html-beginner-challenge-049.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q049-museum-research-abstract-semantic-html-beginner-challenge-049.html</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q050-environment-briefing-story-semantic-html-beginner-challenge-050.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q050-environment-briefing-story-semantic-html-beginner-challenge-050.html</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q051-tech-standards-overview-semantic-html-beginner-challenge-051.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q051-tech-standards-overview-semantic-html-beginner-challenge-051.html</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q052-library-initiative-report-semantic-html-beginner-challenge-052.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q052-library-initiative-report-semantic-html-beginner-challenge-052.html</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q053-civic-update-thread-semantic-html-beginner-challenge-053.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q053-civic-update-thread-semantic-html-beginner-challenge-053.html</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q054-agriculture-innovation-report-semantic-html-beginner-challenge-054.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q054-agriculture-innovation-report-semantic-html-beginner-challenge-054.html</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q055-sports-analysis-editorial-semantic-html-beginner-challenge-055.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q055-sports-analysis-editorial-semantic-html-beginner-challenge-055.html</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q056-cultural-festival-article-semantic-html-beginner-challenge-056.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q056-cultural-festival-article-semantic-html-beginner-challenge-056.html</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q057-medical-procedure-overview-semantic-html-beginner-challenge-057.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q057-medical-procedure-overview-semantic-html-beginner-challenge-057.html</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q058-urban-planning-update-semantic-html-beginner-challenge-058.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q058-urban-planning-update-semantic-html-beginner-challenge-058.html</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q059-learning-roadmap-narrative-semantic-html-beginner-challenge-059.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q059-learning-roadmap-narrative-semantic-html-beginner-challenge-059.html</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/semantic-html/q060-cybersecurity-incident-summary-semantic-html-beginner-challenge-060.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/semantic-html/q060-cybersecurity-incident-summary-semantic-html-beginner-challenge-060.html</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q061-university-admission-application-forms-beginner-challenge-061.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q061-university-admission-application-forms-beginner-challenge-061.html</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q062-job-referral-submission-forms-beginner-challenge-062.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q062-job-referral-submission-forms-beginner-challenge-062.html</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q063-hospital-appointment-intake-forms-beginner-challenge-063.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q063-hospital-appointment-intake-forms-beginner-challenge-063.html</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q064-vacation-leave-request-forms-beginner-challenge-064.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q064-vacation-leave-request-forms-beginner-challenge-064.html</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q065-freelance-project-brief-forms-beginner-challenge-065.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q065-freelance-project-brief-forms-beginner-challenge-065.html</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3574,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q066-startup-demo-registration-forms-beginner-challenge-066.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q066-startup-demo-registration-forms-beginner-challenge-066.html</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q067-scholarship-candidate-form-forms-beginner-challenge-067.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q067-scholarship-candidate-form-forms-beginner-challenge-067.html</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q068-event-speaker-application-forms-beginner-challenge-068.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q068-event-speaker-application-forms-beginner-challenge-068.html</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q069-customer-complaint-intake-forms-beginner-challenge-069.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q069-customer-complaint-intake-forms-beginner-challenge-069.html</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q070-subscription-upgrade-request-forms-beginner-challenge-070.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q070-subscription-upgrade-request-forms-beginner-challenge-070.html</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q071-insurance-claim-entry-forms-beginner-challenge-071.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q071-insurance-claim-entry-forms-beginner-challenge-071.html</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q072-conference-volunteer-signup-forms-beginner-challenge-072.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q072-conference-volunteer-signup-forms-beginner-challenge-072.html</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q073-coaching-session-booking-forms-beginner-challenge-073.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q073-coaching-session-booking-forms-beginner-challenge-073.html</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q074-product-return-request-forms-beginner-challenge-074.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q074-product-return-request-forms-beginner-challenge-074.html</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q075-partnership-proposal-form-forms-beginner-challenge-075.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q075-partnership-proposal-form-forms-beginner-challenge-075.html</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q076-technical-support-escalation-forms-beginner-challenge-076.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q076-technical-support-escalation-forms-beginner-challenge-076.html</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q077-hackathon-team-registration-forms-beginner-challenge-077.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q077-hackathon-team-registration-forms-beginner-challenge-077.html</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q078-course-feedback-survey-forms-beginner-challenge-078.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q078-course-feedback-survey-forms-beginner-challenge-078.html</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q079-housing-rental-inquiry-forms-beginner-challenge-079.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q079-housing-rental-inquiry-forms-beginner-challenge-079.html</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q080-internship-daily-report-forms-beginner-challenge-080.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q080-internship-daily-report-forms-beginner-challenge-080.html</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q081-bank-kyc-update-form-forms-beginner-challenge-081.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q081-bank-kyc-update-form-forms-beginner-challenge-081.html</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q082-restaurant-catering-inquiry-forms-beginner-challenge-082.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q082-restaurant-catering-inquiry-forms-beginner-challenge-082.html</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q083-ngo-volunteer-onboarding-forms-beginner-challenge-083.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q083-ngo-volunteer-onboarding-forms-beginner-challenge-083.html</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q084-workshop-attendance-confirmation-forms-beginner-challenge-084.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q084-workshop-attendance-confirmation-forms-beginner-challenge-084.html</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q085-saas-trial-activation-forms-beginner-challenge-085.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q085-saas-trial-activation-forms-beginner-challenge-085.html</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q086-school-parent-meeting-slot-forms-beginner-challenge-086.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q086-school-parent-meeting-slot-forms-beginner-challenge-086.html</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q087-clinic-lab-test-booking-forms-beginner-challenge-087.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q087-clinic-lab-test-booking-forms-beginner-challenge-087.html</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q088-mentor-mentee-match-form-forms-beginner-challenge-088.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q088-mentor-mentee-match-form-forms-beginner-challenge-088.html</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q089-travel-reimbursement-claim-forms-beginner-challenge-089.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q089-travel-reimbursement-claim-forms-beginner-challenge-089.html</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/forms/q090-research-participation-consent-forms-beginner-challenge-090.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/forms/q090-research-participation-consent-forms-beginner-challenge-090.html</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q091-semester-grade-ledger-tables-beginner-challenge-091.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q091-semester-grade-ledger-tables-beginner-challenge-091.html</t>
         </is>
       </c>
     </row>
@@ -4796,7 +4796,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q092-warehouse-stock-matrix-tables-beginner-challenge-092.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q092-warehouse-stock-matrix-tables-beginner-challenge-092.html</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q093-quarterly-sales-tracker-tables-beginner-challenge-093.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q093-quarterly-sales-tracker-tables-beginner-challenge-093.html</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q094-hospital-shift-allocation-tables-beginner-challenge-094.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q094-hospital-shift-allocation-tables-beginner-challenge-094.html</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q095-flight-departure-board-tables-beginner-challenge-095.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q095-flight-departure-board-tables-beginner-challenge-095.html</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q096-retail-price-comparison-tables-beginner-challenge-096.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q096-retail-price-comparison-tables-beginner-challenge-096.html</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q097-project-sprint-burndown-table-tables-beginner-challenge-097.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q097-project-sprint-burndown-table-tables-beginner-challenge-097.html</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q098-support-sla-performance-tables-beginner-challenge-098.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q098-support-sla-performance-tables-beginner-challenge-098.html</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q099-attendance-compliance-sheet-tables-beginner-challenge-099.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q099-attendance-compliance-sheet-tables-beginner-challenge-099.html</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q100-subscription-renewal-grid-tables-beginner-challenge-100.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q100-subscription-renewal-grid-tables-beginner-challenge-100.html</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q101-website-conversion-report-tables-beginner-challenge-101.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q101-website-conversion-report-tables-beginner-challenge-101.html</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q102-manufacturing-defect-log-tables-beginner-challenge-102.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q102-manufacturing-defect-log-tables-beginner-challenge-102.html</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q103-supplier-delivery-tracker-tables-beginner-challenge-103.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q103-supplier-delivery-tracker-tables-beginner-challenge-103.html</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q104-budget-vs-spend-summary-tables-beginner-challenge-104.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q104-budget-vs-spend-summary-tables-beginner-challenge-104.html</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q105-exam-seating-allocation-tables-beginner-challenge-105.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q105-exam-seating-allocation-tables-beginner-challenge-105.html</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q106-sports-tournament-ladder-tables-beginner-challenge-106.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q106-sports-tournament-ladder-tables-beginner-challenge-106.html</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q107-library-book-circulation-tables-beginner-challenge-107.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q107-library-book-circulation-tables-beginner-challenge-107.html</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q108-class-timetable-board-tables-beginner-challenge-108.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q108-class-timetable-board-tables-beginner-challenge-108.html</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q109-payroll-summary-table-tables-beginner-challenge-109.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q109-payroll-summary-table-tables-beginner-challenge-109.html</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q110-incident-response-timeline-tables-beginner-challenge-110.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q110-incident-response-timeline-tables-beginner-challenge-110.html</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q111-utility-usage-dashboard-table-tables-beginner-challenge-111.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q111-utility-usage-dashboard-table-tables-beginner-challenge-111.html</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q112-training-progress-matrix-tables-beginner-challenge-112.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q112-training-progress-matrix-tables-beginner-challenge-112.html</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q113-marketing-campaign-metrics-tables-beginner-challenge-113.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q113-marketing-campaign-metrics-tables-beginner-challenge-113.html</t>
         </is>
       </c>
     </row>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q114-ecommerce-order-audit-tables-beginner-challenge-114.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q114-ecommerce-order-audit-tables-beginner-challenge-114.html</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q115-research-experiment-log-tables-beginner-challenge-115.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q115-research-experiment-log-tables-beginner-challenge-115.html</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q116-branch-wise-revenue-table-tables-beginner-challenge-116.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q116-branch-wise-revenue-table-tables-beginner-challenge-116.html</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q117-farm-yield-comparison-tables-beginner-challenge-117.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q117-farm-yield-comparison-tables-beginner-challenge-117.html</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q118-transport-route-timings-tables-beginner-challenge-118.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q118-transport-route-timings-tables-beginner-challenge-118.html</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q119-helpdesk-resolution-table-tables-beginner-challenge-119.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q119-helpdesk-resolution-table-tables-beginner-challenge-119.html</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/tables/q120-customer-nps-breakdown-tables-beginner-challenge-120.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/tables/q120-customer-nps-breakdown-tables-beginner-challenge-120.html</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q121-hero-section-theme-build-css-beginner-challenge-121.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q121-hero-section-theme-build-css-beginner-challenge-121.html</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q122-feature-strip-visual-design-css-beginner-challenge-122.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q122-feature-strip-visual-design-css-beginner-challenge-122.html</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q123-announcement-banner-styling-css-beginner-challenge-123.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q123-announcement-banner-styling-css-beginner-challenge-123.html</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q124-profile-card-identity-system-css-beginner-challenge-124.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q124-profile-card-identity-system-css-beginner-challenge-124.html</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q125-navigation-skin-architecture-css-beginner-challenge-125.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q125-navigation-skin-architecture-css-beginner-challenge-125.html</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q126-pricing-tile-skinning-css-beginner-challenge-126.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q126-pricing-tile-skinning-css-beginner-challenge-126.html</t>
         </is>
       </c>
     </row>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q127-dashboard-widget-aesthetics-css-beginner-challenge-127.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q127-dashboard-widget-aesthetics-css-beginner-challenge-127.html</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q128-testimonial-emphasis-style-css-beginner-challenge-128.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q128-testimonial-emphasis-style-css-beginner-challenge-128.html</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q129-alert-severity-theme-pack-css-beginner-challenge-129.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q129-alert-severity-theme-pack-css-beginner-challenge-129.html</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q130-tag-system-color-language-css-beginner-challenge-130.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q130-tag-system-color-language-css-beginner-challenge-130.html</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q131-timeline-accent-styling-css-beginner-challenge-131.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q131-timeline-accent-styling-css-beginner-challenge-131.html</t>
         </is>
       </c>
     </row>
@@ -6676,7 +6676,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q132-footer-visual-hierarchy-css-beginner-challenge-132.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q132-footer-visual-hierarchy-css-beginner-challenge-132.html</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q133-article-typography-refinement-css-beginner-challenge-133.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q133-article-typography-refinement-css-beginner-challenge-133.html</t>
         </is>
       </c>
     </row>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q134-search-panel-interface-look-css-beginner-challenge-134.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q134-search-panel-interface-look-css-beginner-challenge-134.html</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q135-promo-block-contrast-styling-css-beginner-challenge-135.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q135-promo-block-contrast-styling-css-beginner-challenge-135.html</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q136-cta-group-interaction-styling-css-beginner-challenge-136.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q136-cta-group-interaction-styling-css-beginner-challenge-136.html</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q137-section-divider-language-css-beginner-challenge-137.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q137-section-divider-language-css-beginner-challenge-137.html</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q138-stats-counter-appearance-css-beginner-challenge-138.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q138-stats-counter-appearance-css-beginner-challenge-138.html</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q139-form-state-theme-rules-css-beginner-challenge-139.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q139-form-state-theme-rules-css-beginner-challenge-139.html</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q140-sidebar-branding-styles-css-beginner-challenge-140.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q140-sidebar-branding-styles-css-beginner-challenge-140.html</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q141-loading-block-visual-state-css-beginner-challenge-141.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q141-loading-block-visual-state-css-beginner-challenge-141.html</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q142-notification-stack-styling-css-beginner-challenge-142.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q142-notification-stack-styling-css-beginner-challenge-142.html</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q143-badge-priority-color-rules-css-beginner-challenge-143.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q143-badge-priority-color-rules-css-beginner-challenge-143.html</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q144-panel-depth-treatment-css-beginner-challenge-144.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q144-panel-depth-treatment-css-beginner-challenge-144.html</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q145-card-hover-atmosphere-css-beginner-challenge-145.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q145-card-hover-atmosphere-css-beginner-challenge-145.html</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q146-tab-navigation-styling-css-beginner-challenge-146.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q146-tab-navigation-styling-css-beginner-challenge-146.html</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q147-review-block-quote-styling-css-beginner-challenge-147.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q147-review-block-quote-styling-css-beginner-challenge-147.html</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q148-utility-class-theme-set-css-beginner-challenge-148.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q148-utility-class-theme-set-css-beginner-challenge-148.html</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q149-feature-comparison-emphasis-css-beginner-challenge-149.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q149-feature-comparison-emphasis-css-beginner-challenge-149.html</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/css/q150-microcopy-tone-styling-css-beginner-challenge-150.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/css/q150-microcopy-tone-styling-css-beginner-challenge-150.html</t>
         </is>
       </c>
     </row>
@@ -7569,7 +7569,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q151-card-padding-calibration-box-model-beginner-challenge-151.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q151-card-padding-calibration-box-model-beginner-challenge-151.html</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q152-panel-margin-rhythm-box-model-beginner-challenge-152.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q152-panel-margin-rhythm-box-model-beginner-challenge-152.html</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q153-info-tile-border-discipline-box-model-beginner-challenge-153.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q153-info-tile-border-discipline-box-model-beginner-challenge-153.html</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q154-content-column-width-control-box-model-beginner-challenge-154.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q154-content-column-width-control-box-model-beginner-challenge-154.html</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q155-widget-spacing-consistency-box-model-beginner-challenge-155.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q155-widget-spacing-consistency-box-model-beginner-challenge-155.html</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q156-form-field-internal-spacing-box-model-beginner-challenge-156.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q156-form-field-internal-spacing-box-model-beginner-challenge-156.html</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q157-header-to-body-gap-control-box-model-beginner-challenge-157.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q157-header-to-body-gap-control-box-model-beginner-challenge-157.html</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q158-sidebar-item-box-sizing-box-model-beginner-challenge-158.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q158-sidebar-item-box-sizing-box-model-beginner-challenge-158.html</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q159-modal-frame-boundary-setup-box-model-beginner-challenge-159.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q159-modal-frame-boundary-setup-box-model-beginner-challenge-159.html</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q160-cta-block-breathing-space-box-model-beginner-challenge-160.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q160-cta-block-breathing-space-box-model-beginner-challenge-160.html</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q161-list-row-compact-spacing-box-model-beginner-challenge-161.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q161-list-row-compact-spacing-box-model-beginner-challenge-161.html</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q162-avatar-meta-box-framing-box-model-beginner-challenge-162.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q162-avatar-meta-box-framing-box-model-beginner-challenge-162.html</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q163-stats-tile-edge-balance-box-model-beginner-challenge-163.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q163-stats-tile-edge-balance-box-model-beginner-challenge-163.html</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q164-caption-wrapper-width-rules-box-model-beginner-challenge-164.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q164-caption-wrapper-width-rules-box-model-beginner-challenge-164.html</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q165-toolbar-item-separation-box-model-beginner-challenge-165.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q165-toolbar-item-separation-box-model-beginner-challenge-165.html</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q166-section-shell-spacing-scale-box-model-beginner-challenge-166.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q166-section-shell-spacing-scale-box-model-beginner-challenge-166.html</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q167-promo-ribbon-box-balance-box-model-beginner-challenge-167.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q167-promo-ribbon-box-balance-box-model-beginner-challenge-167.html</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q168-article-paragraph-width-guard-box-model-beginner-challenge-168.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q168-article-paragraph-width-guard-box-model-beginner-challenge-168.html</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q169-table-cell-padding-policy-box-model-beginner-challenge-169.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q169-table-cell-padding-policy-box-model-beginner-challenge-169.html</t>
         </is>
       </c>
     </row>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q170-gallery-tile-box-balance-box-model-beginner-challenge-170.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q170-gallery-tile-box-balance-box-model-beginner-challenge-170.html</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q171-notification-container-sizing-box-model-beginner-challenge-171.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q171-notification-container-sizing-box-model-beginner-challenge-171.html</t>
         </is>
       </c>
     </row>
@@ -8556,7 +8556,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q172-pricing-card-edge-rhythm-box-model-beginner-challenge-172.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q172-pricing-card-edge-rhythm-box-model-beginner-challenge-172.html</t>
         </is>
       </c>
     </row>
@@ -8603,7 +8603,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q173-faq-panel-spacing-logic-box-model-beginner-challenge-173.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q173-faq-panel-spacing-logic-box-model-beginner-challenge-173.html</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q174-timeline-node-box-spacing-box-model-beginner-challenge-174.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q174-timeline-node-box-spacing-box-model-beginner-challenge-174.html</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q175-action-bar-padding-grid-box-model-beginner-challenge-175.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q175-action-bar-padding-grid-box-model-beginner-challenge-175.html</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q176-profile-summary-frame-box-model-beginner-challenge-176.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q176-profile-summary-frame-box-model-beginner-challenge-176.html</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q177-comment-box-vertical-rhythm-box-model-beginner-challenge-177.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q177-comment-box-vertical-rhythm-box-model-beginner-challenge-177.html</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q178-checkout-summary-boundaries-box-model-beginner-challenge-178.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q178-checkout-summary-boundaries-box-model-beginner-challenge-178.html</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q179-card-stack-consistent-offsets-box-model-beginner-challenge-179.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q179-card-stack-consistent-offsets-box-model-beginner-challenge-179.html</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/box-model/q180-footer-link-block-sizing-box-model-beginner-challenge-180.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/box-model/q180-footer-link-block-sizing-box-model-beginner-challenge-180.html</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q181-top-nav-distribution-flexbox-beginner-challenge-181.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q181-top-nav-distribution-flexbox-beginner-challenge-181.html</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q182-action-toolbar-alignment-flexbox-beginner-challenge-182.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q182-action-toolbar-alignment-flexbox-beginner-challenge-182.html</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q183-profile-header-justification-flexbox-beginner-challenge-183.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q183-profile-header-justification-flexbox-beginner-challenge-183.html</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q184-card-deck-wrapping-rules-flexbox-beginner-challenge-184.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q184-card-deck-wrapping-rules-flexbox-beginner-challenge-184.html</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q185-pricing-row-equalization-flexbox-beginner-challenge-185.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q185-pricing-row-equalization-flexbox-beginner-challenge-185.html</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9214,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q186-form-controls-inline-layout-flexbox-beginner-challenge-186.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q186-form-controls-inline-layout-flexbox-beginner-challenge-186.html</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q187-comment-header-alignment-flexbox-beginner-challenge-187.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q187-comment-header-alignment-flexbox-beginner-challenge-187.html</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q188-sidebar-menu-distribution-flexbox-beginner-challenge-188.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q188-sidebar-menu-distribution-flexbox-beginner-challenge-188.html</t>
         </is>
       </c>
     </row>
@@ -9355,7 +9355,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q189-mobile-header-flex-shift-flexbox-beginner-challenge-189.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q189-mobile-header-flex-shift-flexbox-beginner-challenge-189.html</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q190-feature-split-justify-pattern-flexbox-beginner-challenge-190.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q190-feature-split-justify-pattern-flexbox-beginner-challenge-190.html</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q191-rating-row-alignment-flexbox-beginner-challenge-191.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q191-rating-row-alignment-flexbox-beginner-challenge-191.html</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q192-media-object-horizontal-flow-flexbox-beginner-challenge-192.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q192-media-object-horizontal-flow-flexbox-beginner-challenge-192.html</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q193-tag-wrap-control-flexbox-beginner-challenge-193.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q193-tag-wrap-control-flexbox-beginner-challenge-193.html</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q194-checkout-totals-alignment-flexbox-beginner-challenge-194.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q194-checkout-totals-alignment-flexbox-beginner-challenge-194.html</t>
         </is>
       </c>
     </row>
@@ -9637,7 +9637,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q195-icon-label-pairing-flexbox-beginner-challenge-195.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q195-icon-label-pairing-flexbox-beginner-challenge-195.html</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q196-gallery-caption-balance-flexbox-beginner-challenge-196.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q196-gallery-caption-balance-flexbox-beginner-challenge-196.html</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q197-task-item-alignment-flexbox-beginner-challenge-197.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q197-task-item-alignment-flexbox-beginner-challenge-197.html</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q198-search-result-action-row-flexbox-beginner-challenge-198.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q198-search-result-action-row-flexbox-beginner-challenge-198.html</t>
         </is>
       </c>
     </row>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q199-sticky-footer-link-alignment-flexbox-beginner-challenge-199.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q199-sticky-footer-link-alignment-flexbox-beginner-challenge-199.html</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q200-kpi-row-distribution-flexbox-beginner-challenge-200.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q200-kpi-row-distribution-flexbox-beginner-challenge-200.html</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q201-avatar-text-baseline-flexbox-beginner-challenge-201.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q201-avatar-text-baseline-flexbox-beginner-challenge-201.html</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q202-button-cluster-wrap-strategy-flexbox-beginner-challenge-202.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q202-button-cluster-wrap-strategy-flexbox-beginner-challenge-202.html</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q203-menu-toggle-spacing-flexbox-beginner-challenge-203.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q203-menu-toggle-spacing-flexbox-beginner-challenge-203.html</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q204-notification-item-alignment-flexbox-beginner-challenge-204.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q204-notification-item-alignment-flexbox-beginner-challenge-204.html</t>
         </is>
       </c>
     </row>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q205-filter-bar-justify-rules-flexbox-beginner-challenge-205.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q205-filter-bar-justify-rules-flexbox-beginner-challenge-205.html</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q206-timeline-row-distribution-flexbox-beginner-challenge-206.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q206-timeline-row-distribution-flexbox-beginner-challenge-206.html</t>
         </is>
       </c>
     </row>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q207-progress-card-content-flow-flexbox-beginner-challenge-207.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q207-progress-card-content-flow-flexbox-beginner-challenge-207.html</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q208-list-item-meta-alignment-flexbox-beginner-challenge-208.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q208-list-item-meta-alignment-flexbox-beginner-challenge-208.html</t>
         </is>
       </c>
     </row>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q209-chat-bubble-row-layout-flexbox-beginner-challenge-209.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q209-chat-bubble-row-layout-flexbox-beginner-challenge-209.html</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/flexbox/q210-hero-cta-group-alignment-flexbox-beginner-challenge-210.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/flexbox/q210-hero-cta-group-alignment-flexbox-beginner-challenge-210.html</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q211-analytics-overview-lattice-grid-beginner-challenge-211.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q211-analytics-overview-lattice-grid-beginner-challenge-211.html</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q212-course-catalog-grid-system-grid-beginner-challenge-212.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q212-course-catalog-grid-system-grid-beginner-challenge-212.html</t>
         </is>
       </c>
     </row>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q213-portfolio-mosaic-grid-grid-beginner-challenge-213.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q213-portfolio-mosaic-grid-grid-beginner-challenge-213.html</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q214-product-shelf-grid-grid-beginner-challenge-214.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q214-product-shelf-grid-grid-beginner-challenge-214.html</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q215-editorial-magazine-grid-grid-beginner-challenge-215.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q215-editorial-magazine-grid-grid-beginner-challenge-215.html</t>
         </is>
       </c>
     </row>
@@ -10624,7 +10624,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q216-admin-console-grid-grid-beginner-challenge-216.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q216-admin-console-grid-grid-beginner-challenge-216.html</t>
         </is>
       </c>
     </row>
@@ -10671,7 +10671,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q217-learning-module-matrix-grid-beginner-challenge-217.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q217-learning-module-matrix-grid-beginner-challenge-217.html</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q218-kpi-snapshot-grid-grid-beginner-challenge-218.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q218-kpi-snapshot-grid-grid-beginner-challenge-218.html</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q219-team-directory-mosaic-grid-beginner-challenge-219.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q219-team-directory-mosaic-grid-beginner-challenge-219.html</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q220-news-digest-grid-frame-grid-beginner-challenge-220.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q220-news-digest-grid-frame-grid-beginner-challenge-220.html</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q221-case-study-showcase-grid-grid-beginner-challenge-221.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q221-case-study-showcase-grid-grid-beginner-challenge-221.html</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q222-calendar-planning-grid-grid-beginner-challenge-222.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q222-calendar-planning-grid-grid-beginner-challenge-222.html</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q223-pricing-matrix-grid-grid-beginner-challenge-223.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q223-pricing-matrix-grid-grid-beginner-challenge-223.html</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q224-service-card-grid-grid-beginner-challenge-224.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q224-service-card-grid-grid-beginner-challenge-224.html</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q225-feature-matrix-alignment-grid-grid-beginner-challenge-225.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q225-feature-matrix-alignment-grid-grid-beginner-challenge-225.html</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q226-sidebar-content-grid-grid-beginner-challenge-226.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q226-sidebar-content-grid-grid-beginner-challenge-226.html</t>
         </is>
       </c>
     </row>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q227-blog-highlight-grid-grid-beginner-challenge-227.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q227-blog-highlight-grid-grid-beginner-challenge-227.html</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q228-stats-and-table-grid-grid-beginner-challenge-228.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q228-stats-and-table-grid-grid-beginner-challenge-228.html</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q229-widget-control-board-grid-grid-beginner-challenge-229.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q229-widget-control-board-grid-grid-beginner-challenge-229.html</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q230-research-summary-grid-grid-beginner-challenge-230.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q230-research-summary-grid-grid-beginner-challenge-230.html</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q231-image-gallery-proportion-grid-grid-beginner-challenge-231.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q231-image-gallery-proportion-grid-grid-beginner-challenge-231.html</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q232-landing-feature-grid-grid-beginner-challenge-232.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q232-landing-feature-grid-grid-beginner-challenge-232.html</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q233-operations-control-grid-grid-beginner-challenge-233.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q233-operations-control-grid-grid-beginner-challenge-233.html</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q234-department-overview-grid-grid-beginner-challenge-234.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q234-department-overview-grid-grid-beginner-challenge-234.html</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q235-schedule-planner-grid-grid-beginner-challenge-235.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q235-schedule-planner-grid-grid-beginner-challenge-235.html</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q236-offer-comparison-grid-grid-beginner-challenge-236.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q236-offer-comparison-grid-grid-beginner-challenge-236.html</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q237-marketplace-listing-grid-grid-beginner-challenge-237.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q237-marketplace-listing-grid-grid-beginner-challenge-237.html</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q238-campaign-results-grid-grid-beginner-challenge-238.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q238-campaign-results-grid-grid-beginner-challenge-238.html</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q239-onboarding-steps-grid-grid-beginner-challenge-239.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q239-onboarding-steps-grid-grid-beginner-challenge-239.html</t>
         </is>
       </c>
     </row>
@@ -11752,7 +11752,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/grid/q240-multi-panel-knowledge-grid-grid-beginner-challenge-240.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/grid/q240-multi-panel-knowledge-grid-grid-beginner-challenge-240.html</t>
         </is>
       </c>
     </row>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q241-breakpoint-driven-nav-shift-media-queries-beginner-challenge-241.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q241-breakpoint-driven-nav-shift-media-queries-beginner-challenge-241.html</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q242-tablet-card-reflow-media-queries-beginner-challenge-242.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q242-tablet-card-reflow-media-queries-beginner-challenge-242.html</t>
         </is>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q243-desktop-typography-expansion-media-queries-beginner-challenge-243.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q243-desktop-typography-expansion-media-queries-beginner-challenge-243.html</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q244-form-stack-conversion-media-queries-beginner-challenge-244.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q244-form-stack-conversion-media-queries-beginner-challenge-244.html</t>
         </is>
       </c>
     </row>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q245-sidebar-collapse-trigger-media-queries-beginner-challenge-245.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q245-sidebar-collapse-trigger-media-queries-beginner-challenge-245.html</t>
         </is>
       </c>
     </row>
@@ -12034,7 +12034,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q246-hero-proportion-change-media-queries-beginner-challenge-246.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q246-hero-proportion-change-media-queries-beginner-challenge-246.html</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12081,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q247-button-group-wrapping-media-queries-beginner-challenge-247.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q247-button-group-wrapping-media-queries-beginner-challenge-247.html</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q248-table-to-card-adaptation-media-queries-beginner-challenge-248.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q248-table-to-card-adaptation-media-queries-beginner-challenge-248.html</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12175,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q249-gallery-column-reduction-media-queries-beginner-challenge-249.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q249-gallery-column-reduction-media-queries-beginner-challenge-249.html</t>
         </is>
       </c>
     </row>
@@ -12222,7 +12222,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q250-footer-stack-breakpoint-media-queries-beginner-challenge-250.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q250-footer-stack-breakpoint-media-queries-beginner-challenge-250.html</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q251-sticky-header-enable-rule-media-queries-beginner-challenge-251.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q251-sticky-header-enable-rule-media-queries-beginner-challenge-251.html</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q252-section-spacing-adaptation-media-queries-beginner-challenge-252.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q252-section-spacing-adaptation-media-queries-beginner-challenge-252.html</t>
         </is>
       </c>
     </row>
@@ -12363,7 +12363,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q253-banner-height-tuning-media-queries-beginner-challenge-253.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q253-banner-height-tuning-media-queries-beginner-challenge-253.html</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q254-cta-position-switch-media-queries-beginner-challenge-254.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q254-cta-position-switch-media-queries-beginner-challenge-254.html</t>
         </is>
       </c>
     </row>
@@ -12457,7 +12457,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q255-grid-area-remap-media-queries-beginner-challenge-255.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q255-grid-area-remap-media-queries-beginner-challenge-255.html</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q256-image-treatment-by-viewport-media-queries-beginner-challenge-256.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q256-image-treatment-by-viewport-media-queries-beginner-challenge-256.html</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q257-input-width-adaptation-media-queries-beginner-challenge-257.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q257-input-width-adaptation-media-queries-beginner-challenge-257.html</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q258-pricing-row-reorder-media-queries-beginner-challenge-258.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q258-pricing-row-reorder-media-queries-beginner-challenge-258.html</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q259-visibility-toggle-by-width-media-queries-beginner-challenge-259.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q259-visibility-toggle-by-width-media-queries-beginner-challenge-259.html</t>
         </is>
       </c>
     </row>
@@ -12692,7 +12692,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q260-dashboard-block-shift-media-queries-beginner-challenge-260.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q260-dashboard-block-shift-media-queries-beginner-challenge-260.html</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q261-two-pane-to-single-pane-media-queries-beginner-challenge-261.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q261-two-pane-to-single-pane-media-queries-beginner-challenge-261.html</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q262-list-density-adaptation-media-queries-beginner-challenge-262.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q262-list-density-adaptation-media-queries-beginner-challenge-262.html</t>
         </is>
       </c>
     </row>
@@ -12833,7 +12833,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q263-metric-card-rearrangement-media-queries-beginner-challenge-263.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q263-metric-card-rearrangement-media-queries-beginner-challenge-263.html</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q264-timeline-simplification-rule-media-queries-beginner-challenge-264.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q264-timeline-simplification-rule-media-queries-beginner-challenge-264.html</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q265-control-panel-collapse-media-queries-beginner-challenge-265.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q265-control-panel-collapse-media-queries-beginner-challenge-265.html</t>
         </is>
       </c>
     </row>
@@ -12974,7 +12974,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q266-search-result-layout-flip-media-queries-beginner-challenge-266.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q266-search-result-layout-flip-media-queries-beginner-challenge-266.html</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13021,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q267-feature-tiles-rebalance-media-queries-beginner-challenge-267.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q267-feature-tiles-rebalance-media-queries-beginner-challenge-267.html</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q268-promo-copy-scaling-media-queries-beginner-challenge-268.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q268-promo-copy-scaling-media-queries-beginner-challenge-268.html</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q269-navigation-hit-area-adjustment-media-queries-beginner-challenge-269.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q269-navigation-hit-area-adjustment-media-queries-beginner-challenge-269.html</t>
         </is>
       </c>
     </row>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/media-queries/q270-mobile-first-layering-conversion-media-queries-beginner-challenge-270.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/media-queries/q270-mobile-first-layering-conversion-media-queries-beginner-challenge-270.html</t>
         </is>
       </c>
     </row>
@@ -13209,7 +13209,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q271-saas-landing-multi-device-build-responsive-design-beginner-challenge-271.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q271-saas-landing-multi-device-build-responsive-design-beginner-challenge-271.html</t>
         </is>
       </c>
     </row>
@@ -13256,7 +13256,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q272-education-portal-adaptive-layout-responsive-design-beginner-challenge-272.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q272-education-portal-adaptive-layout-responsive-design-beginner-challenge-272.html</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q273-clinic-website-fluid-flow-responsive-design-beginner-challenge-273.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q273-clinic-website-fluid-flow-responsive-design-beginner-challenge-273.html</t>
         </is>
       </c>
     </row>
@@ -13350,7 +13350,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-beginner-challenge-274.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-beginner-challenge-274.html</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13397,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q275-travel-guide-responsive-build-responsive-design-beginner-challenge-275.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q275-travel-guide-responsive-build-responsive-design-beginner-challenge-275.html</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q276-portfolio-site-fluid-components-responsive-design-beginner-challenge-276.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q276-portfolio-site-fluid-components-responsive-design-beginner-challenge-276.html</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q277-community-platform-adaptive-shell-responsive-design-beginner-challenge-277.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q277-community-platform-adaptive-shell-responsive-design-beginner-challenge-277.html</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q278-event-website-responsive-frame-responsive-design-beginner-challenge-278.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q278-event-website-responsive-frame-responsive-design-beginner-challenge-278.html</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-beginner-challenge-279.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-beginner-challenge-279.html</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-beginner-challenge-280.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-beginner-challenge-280.html</t>
         </is>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q281-dashboard-adaptive-overview-responsive-design-beginner-challenge-281.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q281-dashboard-adaptive-overview-responsive-design-beginner-challenge-281.html</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q282-booking-interface-responsive-build-responsive-design-beginner-challenge-282.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q282-booking-interface-responsive-build-responsive-design-beginner-challenge-282.html</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-beginner-challenge-283.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-beginner-challenge-283.html</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-beginner-challenge-284.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-beginner-challenge-284.html</t>
         </is>
       </c>
     </row>
@@ -13867,7 +13867,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-beginner-challenge-285.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-beginner-challenge-285.html</t>
         </is>
       </c>
     </row>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q286-help-center-responsive-structure-responsive-design-beginner-challenge-286.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q286-help-center-responsive-structure-responsive-design-beginner-challenge-286.html</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-beginner-challenge-287.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-beginner-challenge-287.html</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q288-course-platform-responsive-cards-responsive-design-beginner-challenge-288.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q288-course-platform-responsive-cards-responsive-design-beginner-challenge-288.html</t>
         </is>
       </c>
     </row>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q289-music-festival-adaptive-layout-responsive-design-beginner-challenge-289.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q289-music-festival-adaptive-layout-responsive-design-beginner-challenge-289.html</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q290-research-portal-responsive-build-responsive-design-beginner-challenge-290.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q290-research-portal-responsive-build-responsive-design-beginner-challenge-290.html</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-beginner-challenge-291.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-beginner-challenge-291.html</t>
         </is>
       </c>
     </row>
@@ -14196,7 +14196,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-beginner-challenge-292.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-beginner-challenge-292.html</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q293-public-service-responsive-site-responsive-design-beginner-challenge-293.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q293-public-service-responsive-site-responsive-design-beginner-challenge-293.html</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-beginner-challenge-294.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-beginner-challenge-294.html</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-beginner-challenge-295.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-beginner-challenge-295.html</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q296-movie-review-responsive-layout-responsive-design-beginner-challenge-296.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q296-movie-review-responsive-layout-responsive-design-beginner-challenge-296.html</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q297-real-estate-adaptive-listing-responsive-design-beginner-challenge-297.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q297-real-estate-adaptive-listing-responsive-design-beginner-challenge-297.html</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-beginner-challenge-298.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-beginner-challenge-298.html</t>
         </is>
       </c>
     </row>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q299-tourism-board-responsive-story-responsive-design-beginner-challenge-299.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q299-tourism-board-responsive-story-responsive-design-beginner-challenge-299.html</t>
         </is>
       </c>
     </row>
@@ -14572,7 +14572,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/beginner/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-beginner-challenge-300.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/beginner/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-beginner-challenge-300.html</t>
         </is>
       </c>
     </row>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q001-portfolio-hero-blueprint-html-intermediate-challenge-001.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q001-portfolio-hero-blueprint-html-intermediate-challenge-001.html</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q002-campus-club-home-structure-html-intermediate-challenge-002.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q002-campus-club-home-structure-html-intermediate-challenge-002.html</t>
         </is>
       </c>
     </row>
@@ -14785,7 +14785,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q003-startup-about-storyline-html-intermediate-challenge-003.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q003-startup-about-storyline-html-intermediate-challenge-003.html</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q004-travel-blog-intro-layout-html-intermediate-challenge-004.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q004-travel-blog-intro-layout-html-intermediate-challenge-004.html</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q005-food-menu-showcase-page-html-intermediate-challenge-005.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q005-food-menu-showcase-page-html-intermediate-challenge-005.html</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q006-course-finder-landing-outline-html-intermediate-challenge-006.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q006-course-finder-landing-outline-html-intermediate-challenge-006.html</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q007-ngo-mission-page-structure-html-intermediate-challenge-007.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q007-ngo-mission-page-structure-html-intermediate-challenge-007.html</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q008-podcast-episode-landing-html-intermediate-challenge-008.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q008-podcast-episode-landing-html-intermediate-challenge-008.html</t>
         </is>
       </c>
     </row>
@@ -15067,7 +15067,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q009-fitness-coach-intro-page-html-intermediate-challenge-009.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q009-fitness-coach-intro-page-html-intermediate-challenge-009.html</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q010-bookstore-discover-page-html-intermediate-challenge-010.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q010-bookstore-discover-page-html-intermediate-challenge-010.html</t>
         </is>
       </c>
     </row>
@@ -15161,7 +15161,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q011-event-countdown-content-page-html-intermediate-challenge-011.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q011-event-countdown-content-page-html-intermediate-challenge-011.html</t>
         </is>
       </c>
     </row>
@@ -15208,7 +15208,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q012-freelancer-service-page-skeleton-html-intermediate-challenge-012.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q012-freelancer-service-page-skeleton-html-intermediate-challenge-012.html</t>
         </is>
       </c>
     </row>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q013-museum-exhibit-intro-page-html-intermediate-challenge-013.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q013-museum-exhibit-intro-page-html-intermediate-challenge-013.html</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q014-career-fair-info-page-html-intermediate-challenge-014.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q014-career-fair-info-page-html-intermediate-challenge-014.html</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q015-tech-meetup-announcement-page-html-intermediate-challenge-015.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q015-tech-meetup-announcement-page-html-intermediate-challenge-015.html</t>
         </is>
       </c>
     </row>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q016-local-news-digest-home-html-intermediate-challenge-016.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q016-local-news-digest-home-html-intermediate-challenge-016.html</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q017-recipe-discovery-landing-html-intermediate-challenge-017.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q017-recipe-discovery-landing-html-intermediate-challenge-017.html</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q018-product-launch-intro-page-html-intermediate-challenge-018.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q018-product-launch-intro-page-html-intermediate-challenge-018.html</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q019-student-project-gallery-page-html-intermediate-challenge-019.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q019-student-project-gallery-page-html-intermediate-challenge-019.html</t>
         </is>
       </c>
     </row>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q020-volunteer-drive-landing-html-intermediate-challenge-020.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q020-volunteer-drive-landing-html-intermediate-challenge-020.html</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q021-language-learning-home-html-intermediate-challenge-021.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q021-language-learning-home-html-intermediate-challenge-021.html</t>
         </is>
       </c>
     </row>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q022-internship-portal-intro-html-intermediate-challenge-022.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q022-internship-portal-intro-html-intermediate-challenge-022.html</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q023-healthcare-awareness-page-html-intermediate-challenge-023.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q023-healthcare-awareness-page-html-intermediate-challenge-023.html</t>
         </is>
       </c>
     </row>
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q024-photography-journey-page-html-intermediate-challenge-024.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q024-photography-journey-page-html-intermediate-challenge-024.html</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q025-coding-bootcamp-info-page-html-intermediate-challenge-025.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q025-coding-bootcamp-info-page-html-intermediate-challenge-025.html</t>
         </is>
       </c>
     </row>
@@ -15866,7 +15866,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q026-town-hall-notice-page-html-intermediate-challenge-026.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q026-town-hall-notice-page-html-intermediate-challenge-026.html</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15913,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q027-scholarship-program-intro-html-intermediate-challenge-027.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q027-scholarship-program-intro-html-intermediate-challenge-027.html</t>
         </is>
       </c>
     </row>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q028-music-festival-welcome-page-html-intermediate-challenge-028.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q028-music-festival-welcome-page-html-intermediate-challenge-028.html</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q029-real-estate-listing-intro-html-intermediate-challenge-029.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q029-real-estate-listing-intro-html-intermediate-challenge-029.html</t>
         </is>
       </c>
     </row>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/html/q030-climate-action-campaign-page-html-intermediate-challenge-030.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/html/q030-climate-action-campaign-page-html-intermediate-challenge-030.html</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q031-accessible-editorial-article-semantic-html-intermediate-challenge-031.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q031-accessible-editorial-article-semantic-html-intermediate-challenge-031.html</t>
         </is>
       </c>
     </row>
@@ -16148,7 +16148,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q032-landmark-rich-government-notice-semantic-html-intermediate-challenge-032.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q032-landmark-rich-government-notice-semantic-html-intermediate-challenge-032.html</t>
         </is>
       </c>
     </row>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q033-research-summary-with-sections-semantic-html-intermediate-challenge-033.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q033-research-summary-with-sections-semantic-html-intermediate-challenge-033.html</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q034-open-source-release-notes-semantic-html-intermediate-challenge-034.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q034-open-source-release-notes-semantic-html-intermediate-challenge-034.html</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q035-health-advisory-bulletin-semantic-html-intermediate-challenge-035.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q035-health-advisory-bulletin-semantic-html-intermediate-challenge-035.html</t>
         </is>
       </c>
     </row>
@@ -16336,7 +16336,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q036-newsroom-feature-with-asides-semantic-html-intermediate-challenge-036.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q036-newsroom-feature-with-asides-semantic-html-intermediate-challenge-036.html</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q037-education-policy-explainer-semantic-html-intermediate-challenge-037.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q037-education-policy-explainer-semantic-html-intermediate-challenge-037.html</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q038-product-case-study-narrative-semantic-html-intermediate-challenge-038.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q038-product-case-study-narrative-semantic-html-intermediate-challenge-038.html</t>
         </is>
       </c>
     </row>
@@ -16477,7 +16477,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q039-conference-report-with-time-data-semantic-html-intermediate-challenge-039.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q039-conference-report-with-time-data-semantic-html-intermediate-challenge-039.html</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q040-community-program-digest-semantic-html-intermediate-challenge-040.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q040-community-program-digest-semantic-html-intermediate-challenge-040.html</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q041-public-service-announcement-semantic-html-intermediate-challenge-041.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q041-public-service-announcement-semantic-html-intermediate-challenge-041.html</t>
         </is>
       </c>
     </row>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q042-digital-magazine-story-flow-semantic-html-intermediate-challenge-042.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q042-digital-magazine-story-flow-semantic-html-intermediate-challenge-042.html</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q043-cinema-review-with-metadata-semantic-html-intermediate-challenge-043.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q043-cinema-review-with-metadata-semantic-html-intermediate-challenge-043.html</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q044-travel-guide-with-highlights-semantic-html-intermediate-challenge-044.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q044-travel-guide-with-highlights-semantic-html-intermediate-challenge-044.html</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q045-charity-report-with-figures-semantic-html-intermediate-challenge-045.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q045-charity-report-with-figures-semantic-html-intermediate-challenge-045.html</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q046-startup-milestone-chronicle-semantic-html-intermediate-challenge-046.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q046-startup-milestone-chronicle-semantic-html-intermediate-challenge-046.html</t>
         </is>
       </c>
     </row>
@@ -16853,7 +16853,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q047-interview-transcript-publication-semantic-html-intermediate-challenge-047.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q047-interview-transcript-publication-semantic-html-intermediate-challenge-047.html</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q048-workshop-recap-article-semantic-html-intermediate-challenge-048.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q048-workshop-recap-article-semantic-html-intermediate-challenge-048.html</t>
         </is>
       </c>
     </row>
@@ -16947,7 +16947,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q049-museum-research-abstract-semantic-html-intermediate-challenge-049.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q049-museum-research-abstract-semantic-html-intermediate-challenge-049.html</t>
         </is>
       </c>
     </row>
@@ -16994,7 +16994,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q050-environment-briefing-story-semantic-html-intermediate-challenge-050.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q050-environment-briefing-story-semantic-html-intermediate-challenge-050.html</t>
         </is>
       </c>
     </row>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q051-tech-standards-overview-semantic-html-intermediate-challenge-051.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q051-tech-standards-overview-semantic-html-intermediate-challenge-051.html</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q052-library-initiative-report-semantic-html-intermediate-challenge-052.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q052-library-initiative-report-semantic-html-intermediate-challenge-052.html</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q053-civic-update-thread-semantic-html-intermediate-challenge-053.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q053-civic-update-thread-semantic-html-intermediate-challenge-053.html</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q054-agriculture-innovation-report-semantic-html-intermediate-challenge-054.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q054-agriculture-innovation-report-semantic-html-intermediate-challenge-054.html</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q055-sports-analysis-editorial-semantic-html-intermediate-challenge-055.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q055-sports-analysis-editorial-semantic-html-intermediate-challenge-055.html</t>
         </is>
       </c>
     </row>
@@ -17276,7 +17276,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q056-cultural-festival-article-semantic-html-intermediate-challenge-056.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q056-cultural-festival-article-semantic-html-intermediate-challenge-056.html</t>
         </is>
       </c>
     </row>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q057-medical-procedure-overview-semantic-html-intermediate-challenge-057.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q057-medical-procedure-overview-semantic-html-intermediate-challenge-057.html</t>
         </is>
       </c>
     </row>
@@ -17370,7 +17370,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q058-urban-planning-update-semantic-html-intermediate-challenge-058.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q058-urban-planning-update-semantic-html-intermediate-challenge-058.html</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q059-learning-roadmap-narrative-semantic-html-intermediate-challenge-059.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q059-learning-roadmap-narrative-semantic-html-intermediate-challenge-059.html</t>
         </is>
       </c>
     </row>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/semantic-html/q060-cybersecurity-incident-summary-semantic-html-intermediate-challenge-060.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/semantic-html/q060-cybersecurity-incident-summary-semantic-html-intermediate-challenge-060.html</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q061-university-admission-application-forms-intermediate-challenge-061.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q061-university-admission-application-forms-intermediate-challenge-061.html</t>
         </is>
       </c>
     </row>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q062-job-referral-submission-forms-intermediate-challenge-062.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q062-job-referral-submission-forms-intermediate-challenge-062.html</t>
         </is>
       </c>
     </row>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q063-hospital-appointment-intake-forms-intermediate-challenge-063.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q063-hospital-appointment-intake-forms-intermediate-challenge-063.html</t>
         </is>
       </c>
     </row>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q064-vacation-leave-request-forms-intermediate-challenge-064.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q064-vacation-leave-request-forms-intermediate-challenge-064.html</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q065-freelance-project-brief-forms-intermediate-challenge-065.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q065-freelance-project-brief-forms-intermediate-challenge-065.html</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q066-startup-demo-registration-forms-intermediate-challenge-066.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q066-startup-demo-registration-forms-intermediate-challenge-066.html</t>
         </is>
       </c>
     </row>
@@ -17793,7 +17793,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q067-scholarship-candidate-form-forms-intermediate-challenge-067.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q067-scholarship-candidate-form-forms-intermediate-challenge-067.html</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q068-event-speaker-application-forms-intermediate-challenge-068.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q068-event-speaker-application-forms-intermediate-challenge-068.html</t>
         </is>
       </c>
     </row>
@@ -17887,7 +17887,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q069-customer-complaint-intake-forms-intermediate-challenge-069.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q069-customer-complaint-intake-forms-intermediate-challenge-069.html</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q070-subscription-upgrade-request-forms-intermediate-challenge-070.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q070-subscription-upgrade-request-forms-intermediate-challenge-070.html</t>
         </is>
       </c>
     </row>
@@ -17981,7 +17981,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q071-insurance-claim-entry-forms-intermediate-challenge-071.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q071-insurance-claim-entry-forms-intermediate-challenge-071.html</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q072-conference-volunteer-signup-forms-intermediate-challenge-072.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q072-conference-volunteer-signup-forms-intermediate-challenge-072.html</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q073-coaching-session-booking-forms-intermediate-challenge-073.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q073-coaching-session-booking-forms-intermediate-challenge-073.html</t>
         </is>
       </c>
     </row>
@@ -18122,7 +18122,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q074-product-return-request-forms-intermediate-challenge-074.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q074-product-return-request-forms-intermediate-challenge-074.html</t>
         </is>
       </c>
     </row>
@@ -18169,7 +18169,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q075-partnership-proposal-form-forms-intermediate-challenge-075.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q075-partnership-proposal-form-forms-intermediate-challenge-075.html</t>
         </is>
       </c>
     </row>
@@ -18216,7 +18216,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q076-technical-support-escalation-forms-intermediate-challenge-076.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q076-technical-support-escalation-forms-intermediate-challenge-076.html</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q077-hackathon-team-registration-forms-intermediate-challenge-077.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q077-hackathon-team-registration-forms-intermediate-challenge-077.html</t>
         </is>
       </c>
     </row>
@@ -18310,7 +18310,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q078-course-feedback-survey-forms-intermediate-challenge-078.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q078-course-feedback-survey-forms-intermediate-challenge-078.html</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q079-housing-rental-inquiry-forms-intermediate-challenge-079.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q079-housing-rental-inquiry-forms-intermediate-challenge-079.html</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q080-internship-daily-report-forms-intermediate-challenge-080.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q080-internship-daily-report-forms-intermediate-challenge-080.html</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q081-bank-kyc-update-form-forms-intermediate-challenge-081.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q081-bank-kyc-update-form-forms-intermediate-challenge-081.html</t>
         </is>
       </c>
     </row>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q082-restaurant-catering-inquiry-forms-intermediate-challenge-082.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q082-restaurant-catering-inquiry-forms-intermediate-challenge-082.html</t>
         </is>
       </c>
     </row>
@@ -18545,7 +18545,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q083-ngo-volunteer-onboarding-forms-intermediate-challenge-083.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q083-ngo-volunteer-onboarding-forms-intermediate-challenge-083.html</t>
         </is>
       </c>
     </row>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q084-workshop-attendance-confirmation-forms-intermediate-challenge-084.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q084-workshop-attendance-confirmation-forms-intermediate-challenge-084.html</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q085-saas-trial-activation-forms-intermediate-challenge-085.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q085-saas-trial-activation-forms-intermediate-challenge-085.html</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q086-school-parent-meeting-slot-forms-intermediate-challenge-086.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q086-school-parent-meeting-slot-forms-intermediate-challenge-086.html</t>
         </is>
       </c>
     </row>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q087-clinic-lab-test-booking-forms-intermediate-challenge-087.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q087-clinic-lab-test-booking-forms-intermediate-challenge-087.html</t>
         </is>
       </c>
     </row>
@@ -18780,7 +18780,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q088-mentor-mentee-match-form-forms-intermediate-challenge-088.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q088-mentor-mentee-match-form-forms-intermediate-challenge-088.html</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18827,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q089-travel-reimbursement-claim-forms-intermediate-challenge-089.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q089-travel-reimbursement-claim-forms-intermediate-challenge-089.html</t>
         </is>
       </c>
     </row>
@@ -18874,7 +18874,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/forms/q090-research-participation-consent-forms-intermediate-challenge-090.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/forms/q090-research-participation-consent-forms-intermediate-challenge-090.html</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q091-semester-grade-ledger-tables-intermediate-challenge-091.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q091-semester-grade-ledger-tables-intermediate-challenge-091.html</t>
         </is>
       </c>
     </row>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q092-warehouse-stock-matrix-tables-intermediate-challenge-092.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q092-warehouse-stock-matrix-tables-intermediate-challenge-092.html</t>
         </is>
       </c>
     </row>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q093-quarterly-sales-tracker-tables-intermediate-challenge-093.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q093-quarterly-sales-tracker-tables-intermediate-challenge-093.html</t>
         </is>
       </c>
     </row>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q094-hospital-shift-allocation-tables-intermediate-challenge-094.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q094-hospital-shift-allocation-tables-intermediate-challenge-094.html</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19109,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q095-flight-departure-board-tables-intermediate-challenge-095.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q095-flight-departure-board-tables-intermediate-challenge-095.html</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q096-retail-price-comparison-tables-intermediate-challenge-096.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q096-retail-price-comparison-tables-intermediate-challenge-096.html</t>
         </is>
       </c>
     </row>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q097-project-sprint-burndown-table-tables-intermediate-challenge-097.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q097-project-sprint-burndown-table-tables-intermediate-challenge-097.html</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q098-support-sla-performance-tables-intermediate-challenge-098.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q098-support-sla-performance-tables-intermediate-challenge-098.html</t>
         </is>
       </c>
     </row>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q099-attendance-compliance-sheet-tables-intermediate-challenge-099.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q099-attendance-compliance-sheet-tables-intermediate-challenge-099.html</t>
         </is>
       </c>
     </row>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q100-subscription-renewal-grid-tables-intermediate-challenge-100.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q100-subscription-renewal-grid-tables-intermediate-challenge-100.html</t>
         </is>
       </c>
     </row>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q101-website-conversion-report-tables-intermediate-challenge-101.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q101-website-conversion-report-tables-intermediate-challenge-101.html</t>
         </is>
       </c>
     </row>
@@ -19438,7 +19438,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q102-manufacturing-defect-log-tables-intermediate-challenge-102.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q102-manufacturing-defect-log-tables-intermediate-challenge-102.html</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q103-supplier-delivery-tracker-tables-intermediate-challenge-103.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q103-supplier-delivery-tracker-tables-intermediate-challenge-103.html</t>
         </is>
       </c>
     </row>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q104-budget-vs-spend-summary-tables-intermediate-challenge-104.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q104-budget-vs-spend-summary-tables-intermediate-challenge-104.html</t>
         </is>
       </c>
     </row>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q105-exam-seating-allocation-tables-intermediate-challenge-105.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q105-exam-seating-allocation-tables-intermediate-challenge-105.html</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q106-sports-tournament-ladder-tables-intermediate-challenge-106.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q106-sports-tournament-ladder-tables-intermediate-challenge-106.html</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q107-library-book-circulation-tables-intermediate-challenge-107.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q107-library-book-circulation-tables-intermediate-challenge-107.html</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q108-class-timetable-board-tables-intermediate-challenge-108.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q108-class-timetable-board-tables-intermediate-challenge-108.html</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q109-payroll-summary-table-tables-intermediate-challenge-109.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q109-payroll-summary-table-tables-intermediate-challenge-109.html</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q110-incident-response-timeline-tables-intermediate-challenge-110.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q110-incident-response-timeline-tables-intermediate-challenge-110.html</t>
         </is>
       </c>
     </row>
@@ -19861,7 +19861,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q111-utility-usage-dashboard-table-tables-intermediate-challenge-111.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q111-utility-usage-dashboard-table-tables-intermediate-challenge-111.html</t>
         </is>
       </c>
     </row>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q112-training-progress-matrix-tables-intermediate-challenge-112.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q112-training-progress-matrix-tables-intermediate-challenge-112.html</t>
         </is>
       </c>
     </row>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q113-marketing-campaign-metrics-tables-intermediate-challenge-113.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q113-marketing-campaign-metrics-tables-intermediate-challenge-113.html</t>
         </is>
       </c>
     </row>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q114-ecommerce-order-audit-tables-intermediate-challenge-114.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q114-ecommerce-order-audit-tables-intermediate-challenge-114.html</t>
         </is>
       </c>
     </row>
@@ -20049,7 +20049,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q115-research-experiment-log-tables-intermediate-challenge-115.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q115-research-experiment-log-tables-intermediate-challenge-115.html</t>
         </is>
       </c>
     </row>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q116-branch-wise-revenue-table-tables-intermediate-challenge-116.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q116-branch-wise-revenue-table-tables-intermediate-challenge-116.html</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q117-farm-yield-comparison-tables-intermediate-challenge-117.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q117-farm-yield-comparison-tables-intermediate-challenge-117.html</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20190,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q118-transport-route-timings-tables-intermediate-challenge-118.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q118-transport-route-timings-tables-intermediate-challenge-118.html</t>
         </is>
       </c>
     </row>
@@ -20237,7 +20237,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q119-helpdesk-resolution-table-tables-intermediate-challenge-119.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q119-helpdesk-resolution-table-tables-intermediate-challenge-119.html</t>
         </is>
       </c>
     </row>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/tables/q120-customer-nps-breakdown-tables-intermediate-challenge-120.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/tables/q120-customer-nps-breakdown-tables-intermediate-challenge-120.html</t>
         </is>
       </c>
     </row>
@@ -20331,7 +20331,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q121-hero-section-theme-build-css-intermediate-challenge-121.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q121-hero-section-theme-build-css-intermediate-challenge-121.html</t>
         </is>
       </c>
     </row>
@@ -20378,7 +20378,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q122-feature-strip-visual-design-css-intermediate-challenge-122.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q122-feature-strip-visual-design-css-intermediate-challenge-122.html</t>
         </is>
       </c>
     </row>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q123-announcement-banner-styling-css-intermediate-challenge-123.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q123-announcement-banner-styling-css-intermediate-challenge-123.html</t>
         </is>
       </c>
     </row>
@@ -20472,7 +20472,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q124-profile-card-identity-system-css-intermediate-challenge-124.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q124-profile-card-identity-system-css-intermediate-challenge-124.html</t>
         </is>
       </c>
     </row>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q125-navigation-skin-architecture-css-intermediate-challenge-125.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q125-navigation-skin-architecture-css-intermediate-challenge-125.html</t>
         </is>
       </c>
     </row>
@@ -20566,7 +20566,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q126-pricing-tile-skinning-css-intermediate-challenge-126.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q126-pricing-tile-skinning-css-intermediate-challenge-126.html</t>
         </is>
       </c>
     </row>
@@ -20613,7 +20613,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q127-dashboard-widget-aesthetics-css-intermediate-challenge-127.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q127-dashboard-widget-aesthetics-css-intermediate-challenge-127.html</t>
         </is>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q128-testimonial-emphasis-style-css-intermediate-challenge-128.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q128-testimonial-emphasis-style-css-intermediate-challenge-128.html</t>
         </is>
       </c>
     </row>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q129-alert-severity-theme-pack-css-intermediate-challenge-129.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q129-alert-severity-theme-pack-css-intermediate-challenge-129.html</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q130-tag-system-color-language-css-intermediate-challenge-130.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q130-tag-system-color-language-css-intermediate-challenge-130.html</t>
         </is>
       </c>
     </row>
@@ -20801,7 +20801,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q131-timeline-accent-styling-css-intermediate-challenge-131.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q131-timeline-accent-styling-css-intermediate-challenge-131.html</t>
         </is>
       </c>
     </row>
@@ -20848,7 +20848,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q132-footer-visual-hierarchy-css-intermediate-challenge-132.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q132-footer-visual-hierarchy-css-intermediate-challenge-132.html</t>
         </is>
       </c>
     </row>
@@ -20895,7 +20895,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q133-article-typography-refinement-css-intermediate-challenge-133.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q133-article-typography-refinement-css-intermediate-challenge-133.html</t>
         </is>
       </c>
     </row>
@@ -20942,7 +20942,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q134-search-panel-interface-look-css-intermediate-challenge-134.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q134-search-panel-interface-look-css-intermediate-challenge-134.html</t>
         </is>
       </c>
     </row>
@@ -20989,7 +20989,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q135-promo-block-contrast-styling-css-intermediate-challenge-135.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q135-promo-block-contrast-styling-css-intermediate-challenge-135.html</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q136-cta-group-interaction-styling-css-intermediate-challenge-136.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q136-cta-group-interaction-styling-css-intermediate-challenge-136.html</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q137-section-divider-language-css-intermediate-challenge-137.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q137-section-divider-language-css-intermediate-challenge-137.html</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q138-stats-counter-appearance-css-intermediate-challenge-138.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q138-stats-counter-appearance-css-intermediate-challenge-138.html</t>
         </is>
       </c>
     </row>
@@ -21177,7 +21177,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q139-form-state-theme-rules-css-intermediate-challenge-139.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q139-form-state-theme-rules-css-intermediate-challenge-139.html</t>
         </is>
       </c>
     </row>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q140-sidebar-branding-styles-css-intermediate-challenge-140.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q140-sidebar-branding-styles-css-intermediate-challenge-140.html</t>
         </is>
       </c>
     </row>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q141-loading-block-visual-state-css-intermediate-challenge-141.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q141-loading-block-visual-state-css-intermediate-challenge-141.html</t>
         </is>
       </c>
     </row>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q142-notification-stack-styling-css-intermediate-challenge-142.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q142-notification-stack-styling-css-intermediate-challenge-142.html</t>
         </is>
       </c>
     </row>
@@ -21365,7 +21365,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q143-badge-priority-color-rules-css-intermediate-challenge-143.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q143-badge-priority-color-rules-css-intermediate-challenge-143.html</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q144-panel-depth-treatment-css-intermediate-challenge-144.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q144-panel-depth-treatment-css-intermediate-challenge-144.html</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21459,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q145-card-hover-atmosphere-css-intermediate-challenge-145.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q145-card-hover-atmosphere-css-intermediate-challenge-145.html</t>
         </is>
       </c>
     </row>
@@ -21506,7 +21506,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q146-tab-navigation-styling-css-intermediate-challenge-146.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q146-tab-navigation-styling-css-intermediate-challenge-146.html</t>
         </is>
       </c>
     </row>
@@ -21553,7 +21553,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q147-review-block-quote-styling-css-intermediate-challenge-147.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q147-review-block-quote-styling-css-intermediate-challenge-147.html</t>
         </is>
       </c>
     </row>
@@ -21600,7 +21600,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q148-utility-class-theme-set-css-intermediate-challenge-148.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q148-utility-class-theme-set-css-intermediate-challenge-148.html</t>
         </is>
       </c>
     </row>
@@ -21647,7 +21647,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q149-feature-comparison-emphasis-css-intermediate-challenge-149.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q149-feature-comparison-emphasis-css-intermediate-challenge-149.html</t>
         </is>
       </c>
     </row>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/css/q150-microcopy-tone-styling-css-intermediate-challenge-150.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/css/q150-microcopy-tone-styling-css-intermediate-challenge-150.html</t>
         </is>
       </c>
     </row>
@@ -21741,7 +21741,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q151-card-padding-calibration-box-model-intermediate-challenge-151.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q151-card-padding-calibration-box-model-intermediate-challenge-151.html</t>
         </is>
       </c>
     </row>
@@ -21788,7 +21788,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q152-panel-margin-rhythm-box-model-intermediate-challenge-152.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q152-panel-margin-rhythm-box-model-intermediate-challenge-152.html</t>
         </is>
       </c>
     </row>
@@ -21835,7 +21835,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q153-info-tile-border-discipline-box-model-intermediate-challenge-153.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q153-info-tile-border-discipline-box-model-intermediate-challenge-153.html</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21882,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q154-content-column-width-control-box-model-intermediate-challenge-154.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q154-content-column-width-control-box-model-intermediate-challenge-154.html</t>
         </is>
       </c>
     </row>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q155-widget-spacing-consistency-box-model-intermediate-challenge-155.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q155-widget-spacing-consistency-box-model-intermediate-challenge-155.html</t>
         </is>
       </c>
     </row>
@@ -21976,7 +21976,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q156-form-field-internal-spacing-box-model-intermediate-challenge-156.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q156-form-field-internal-spacing-box-model-intermediate-challenge-156.html</t>
         </is>
       </c>
     </row>
@@ -22023,7 +22023,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q157-header-to-body-gap-control-box-model-intermediate-challenge-157.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q157-header-to-body-gap-control-box-model-intermediate-challenge-157.html</t>
         </is>
       </c>
     </row>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q158-sidebar-item-box-sizing-box-model-intermediate-challenge-158.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q158-sidebar-item-box-sizing-box-model-intermediate-challenge-158.html</t>
         </is>
       </c>
     </row>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q159-modal-frame-boundary-setup-box-model-intermediate-challenge-159.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q159-modal-frame-boundary-setup-box-model-intermediate-challenge-159.html</t>
         </is>
       </c>
     </row>
@@ -22164,7 +22164,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q160-cta-block-breathing-space-box-model-intermediate-challenge-160.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q160-cta-block-breathing-space-box-model-intermediate-challenge-160.html</t>
         </is>
       </c>
     </row>
@@ -22211,7 +22211,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q161-list-row-compact-spacing-box-model-intermediate-challenge-161.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q161-list-row-compact-spacing-box-model-intermediate-challenge-161.html</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22258,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q162-avatar-meta-box-framing-box-model-intermediate-challenge-162.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q162-avatar-meta-box-framing-box-model-intermediate-challenge-162.html</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q163-stats-tile-edge-balance-box-model-intermediate-challenge-163.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q163-stats-tile-edge-balance-box-model-intermediate-challenge-163.html</t>
         </is>
       </c>
     </row>
@@ -22352,7 +22352,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q164-caption-wrapper-width-rules-box-model-intermediate-challenge-164.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q164-caption-wrapper-width-rules-box-model-intermediate-challenge-164.html</t>
         </is>
       </c>
     </row>
@@ -22399,7 +22399,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q165-toolbar-item-separation-box-model-intermediate-challenge-165.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q165-toolbar-item-separation-box-model-intermediate-challenge-165.html</t>
         </is>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q166-section-shell-spacing-scale-box-model-intermediate-challenge-166.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q166-section-shell-spacing-scale-box-model-intermediate-challenge-166.html</t>
         </is>
       </c>
     </row>
@@ -22493,7 +22493,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q167-promo-ribbon-box-balance-box-model-intermediate-challenge-167.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q167-promo-ribbon-box-balance-box-model-intermediate-challenge-167.html</t>
         </is>
       </c>
     </row>
@@ -22540,7 +22540,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q168-article-paragraph-width-guard-box-model-intermediate-challenge-168.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q168-article-paragraph-width-guard-box-model-intermediate-challenge-168.html</t>
         </is>
       </c>
     </row>
@@ -22587,7 +22587,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q169-table-cell-padding-policy-box-model-intermediate-challenge-169.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q169-table-cell-padding-policy-box-model-intermediate-challenge-169.html</t>
         </is>
       </c>
     </row>
@@ -22634,7 +22634,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q170-gallery-tile-box-balance-box-model-intermediate-challenge-170.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q170-gallery-tile-box-balance-box-model-intermediate-challenge-170.html</t>
         </is>
       </c>
     </row>
@@ -22681,7 +22681,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q171-notification-container-sizing-box-model-intermediate-challenge-171.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q171-notification-container-sizing-box-model-intermediate-challenge-171.html</t>
         </is>
       </c>
     </row>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q172-pricing-card-edge-rhythm-box-model-intermediate-challenge-172.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q172-pricing-card-edge-rhythm-box-model-intermediate-challenge-172.html</t>
         </is>
       </c>
     </row>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q173-faq-panel-spacing-logic-box-model-intermediate-challenge-173.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q173-faq-panel-spacing-logic-box-model-intermediate-challenge-173.html</t>
         </is>
       </c>
     </row>
@@ -22822,7 +22822,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q174-timeline-node-box-spacing-box-model-intermediate-challenge-174.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q174-timeline-node-box-spacing-box-model-intermediate-challenge-174.html</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q175-action-bar-padding-grid-box-model-intermediate-challenge-175.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q175-action-bar-padding-grid-box-model-intermediate-challenge-175.html</t>
         </is>
       </c>
     </row>
@@ -22916,7 +22916,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q176-profile-summary-frame-box-model-intermediate-challenge-176.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q176-profile-summary-frame-box-model-intermediate-challenge-176.html</t>
         </is>
       </c>
     </row>
@@ -22963,7 +22963,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q177-comment-box-vertical-rhythm-box-model-intermediate-challenge-177.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q177-comment-box-vertical-rhythm-box-model-intermediate-challenge-177.html</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q178-checkout-summary-boundaries-box-model-intermediate-challenge-178.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q178-checkout-summary-boundaries-box-model-intermediate-challenge-178.html</t>
         </is>
       </c>
     </row>
@@ -23057,7 +23057,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q179-card-stack-consistent-offsets-box-model-intermediate-challenge-179.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q179-card-stack-consistent-offsets-box-model-intermediate-challenge-179.html</t>
         </is>
       </c>
     </row>
@@ -23104,7 +23104,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/box-model/q180-footer-link-block-sizing-box-model-intermediate-challenge-180.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/box-model/q180-footer-link-block-sizing-box-model-intermediate-challenge-180.html</t>
         </is>
       </c>
     </row>
@@ -23151,7 +23151,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q181-top-nav-distribution-flexbox-intermediate-challenge-181.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q181-top-nav-distribution-flexbox-intermediate-challenge-181.html</t>
         </is>
       </c>
     </row>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q182-action-toolbar-alignment-flexbox-intermediate-challenge-182.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q182-action-toolbar-alignment-flexbox-intermediate-challenge-182.html</t>
         </is>
       </c>
     </row>
@@ -23245,7 +23245,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q183-profile-header-justification-flexbox-intermediate-challenge-183.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q183-profile-header-justification-flexbox-intermediate-challenge-183.html</t>
         </is>
       </c>
     </row>
@@ -23292,7 +23292,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q184-card-deck-wrapping-rules-flexbox-intermediate-challenge-184.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q184-card-deck-wrapping-rules-flexbox-intermediate-challenge-184.html</t>
         </is>
       </c>
     </row>
@@ -23339,7 +23339,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q185-pricing-row-equalization-flexbox-intermediate-challenge-185.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q185-pricing-row-equalization-flexbox-intermediate-challenge-185.html</t>
         </is>
       </c>
     </row>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q186-form-controls-inline-layout-flexbox-intermediate-challenge-186.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q186-form-controls-inline-layout-flexbox-intermediate-challenge-186.html</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q187-comment-header-alignment-flexbox-intermediate-challenge-187.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q187-comment-header-alignment-flexbox-intermediate-challenge-187.html</t>
         </is>
       </c>
     </row>
@@ -23480,7 +23480,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q188-sidebar-menu-distribution-flexbox-intermediate-challenge-188.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q188-sidebar-menu-distribution-flexbox-intermediate-challenge-188.html</t>
         </is>
       </c>
     </row>
@@ -23527,7 +23527,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q189-mobile-header-flex-shift-flexbox-intermediate-challenge-189.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q189-mobile-header-flex-shift-flexbox-intermediate-challenge-189.html</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q190-feature-split-justify-pattern-flexbox-intermediate-challenge-190.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q190-feature-split-justify-pattern-flexbox-intermediate-challenge-190.html</t>
         </is>
       </c>
     </row>
@@ -23621,7 +23621,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q191-rating-row-alignment-flexbox-intermediate-challenge-191.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q191-rating-row-alignment-flexbox-intermediate-challenge-191.html</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23668,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q192-media-object-horizontal-flow-flexbox-intermediate-challenge-192.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q192-media-object-horizontal-flow-flexbox-intermediate-challenge-192.html</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q193-tag-wrap-control-flexbox-intermediate-challenge-193.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q193-tag-wrap-control-flexbox-intermediate-challenge-193.html</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q194-checkout-totals-alignment-flexbox-intermediate-challenge-194.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q194-checkout-totals-alignment-flexbox-intermediate-challenge-194.html</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q195-icon-label-pairing-flexbox-intermediate-challenge-195.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q195-icon-label-pairing-flexbox-intermediate-challenge-195.html</t>
         </is>
       </c>
     </row>
@@ -23856,7 +23856,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q196-gallery-caption-balance-flexbox-intermediate-challenge-196.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q196-gallery-caption-balance-flexbox-intermediate-challenge-196.html</t>
         </is>
       </c>
     </row>
@@ -23903,7 +23903,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q197-task-item-alignment-flexbox-intermediate-challenge-197.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q197-task-item-alignment-flexbox-intermediate-challenge-197.html</t>
         </is>
       </c>
     </row>
@@ -23950,7 +23950,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q198-search-result-action-row-flexbox-intermediate-challenge-198.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q198-search-result-action-row-flexbox-intermediate-challenge-198.html</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q199-sticky-footer-link-alignment-flexbox-intermediate-challenge-199.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q199-sticky-footer-link-alignment-flexbox-intermediate-challenge-199.html</t>
         </is>
       </c>
     </row>
@@ -24044,7 +24044,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q200-kpi-row-distribution-flexbox-intermediate-challenge-200.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q200-kpi-row-distribution-flexbox-intermediate-challenge-200.html</t>
         </is>
       </c>
     </row>
@@ -24091,7 +24091,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q201-avatar-text-baseline-flexbox-intermediate-challenge-201.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q201-avatar-text-baseline-flexbox-intermediate-challenge-201.html</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24138,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q202-button-cluster-wrap-strategy-flexbox-intermediate-challenge-202.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q202-button-cluster-wrap-strategy-flexbox-intermediate-challenge-202.html</t>
         </is>
       </c>
     </row>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q203-menu-toggle-spacing-flexbox-intermediate-challenge-203.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q203-menu-toggle-spacing-flexbox-intermediate-challenge-203.html</t>
         </is>
       </c>
     </row>
@@ -24232,7 +24232,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q204-notification-item-alignment-flexbox-intermediate-challenge-204.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q204-notification-item-alignment-flexbox-intermediate-challenge-204.html</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24279,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q205-filter-bar-justify-rules-flexbox-intermediate-challenge-205.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q205-filter-bar-justify-rules-flexbox-intermediate-challenge-205.html</t>
         </is>
       </c>
     </row>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q206-timeline-row-distribution-flexbox-intermediate-challenge-206.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q206-timeline-row-distribution-flexbox-intermediate-challenge-206.html</t>
         </is>
       </c>
     </row>
@@ -24373,7 +24373,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q207-progress-card-content-flow-flexbox-intermediate-challenge-207.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q207-progress-card-content-flow-flexbox-intermediate-challenge-207.html</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24420,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q208-list-item-meta-alignment-flexbox-intermediate-challenge-208.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q208-list-item-meta-alignment-flexbox-intermediate-challenge-208.html</t>
         </is>
       </c>
     </row>
@@ -24467,7 +24467,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q209-chat-bubble-row-layout-flexbox-intermediate-challenge-209.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q209-chat-bubble-row-layout-flexbox-intermediate-challenge-209.html</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/flexbox/q210-hero-cta-group-alignment-flexbox-intermediate-challenge-210.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/flexbox/q210-hero-cta-group-alignment-flexbox-intermediate-challenge-210.html</t>
         </is>
       </c>
     </row>
@@ -24561,7 +24561,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q211-analytics-overview-lattice-grid-intermediate-challenge-211.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q211-analytics-overview-lattice-grid-intermediate-challenge-211.html</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q212-course-catalog-grid-system-grid-intermediate-challenge-212.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q212-course-catalog-grid-system-grid-intermediate-challenge-212.html</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24655,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q213-portfolio-mosaic-grid-grid-intermediate-challenge-213.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q213-portfolio-mosaic-grid-grid-intermediate-challenge-213.html</t>
         </is>
       </c>
     </row>
@@ -24702,7 +24702,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q214-product-shelf-grid-grid-intermediate-challenge-214.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q214-product-shelf-grid-grid-intermediate-challenge-214.html</t>
         </is>
       </c>
     </row>
@@ -24749,7 +24749,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q215-editorial-magazine-grid-grid-intermediate-challenge-215.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q215-editorial-magazine-grid-grid-intermediate-challenge-215.html</t>
         </is>
       </c>
     </row>
@@ -24796,7 +24796,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q216-admin-console-grid-grid-intermediate-challenge-216.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q216-admin-console-grid-grid-intermediate-challenge-216.html</t>
         </is>
       </c>
     </row>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q217-learning-module-matrix-grid-intermediate-challenge-217.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q217-learning-module-matrix-grid-intermediate-challenge-217.html</t>
         </is>
       </c>
     </row>
@@ -24890,7 +24890,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q218-kpi-snapshot-grid-grid-intermediate-challenge-218.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q218-kpi-snapshot-grid-grid-intermediate-challenge-218.html</t>
         </is>
       </c>
     </row>
@@ -24937,7 +24937,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q219-team-directory-mosaic-grid-intermediate-challenge-219.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q219-team-directory-mosaic-grid-intermediate-challenge-219.html</t>
         </is>
       </c>
     </row>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q220-news-digest-grid-frame-grid-intermediate-challenge-220.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q220-news-digest-grid-frame-grid-intermediate-challenge-220.html</t>
         </is>
       </c>
     </row>
@@ -25031,7 +25031,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q221-case-study-showcase-grid-grid-intermediate-challenge-221.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q221-case-study-showcase-grid-grid-intermediate-challenge-221.html</t>
         </is>
       </c>
     </row>
@@ -25078,7 +25078,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q222-calendar-planning-grid-grid-intermediate-challenge-222.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q222-calendar-planning-grid-grid-intermediate-challenge-222.html</t>
         </is>
       </c>
     </row>
@@ -25125,7 +25125,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q223-pricing-matrix-grid-grid-intermediate-challenge-223.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q223-pricing-matrix-grid-grid-intermediate-challenge-223.html</t>
         </is>
       </c>
     </row>
@@ -25172,7 +25172,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q224-service-card-grid-grid-intermediate-challenge-224.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q224-service-card-grid-grid-intermediate-challenge-224.html</t>
         </is>
       </c>
     </row>
@@ -25219,7 +25219,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q225-feature-matrix-alignment-grid-grid-intermediate-challenge-225.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q225-feature-matrix-alignment-grid-grid-intermediate-challenge-225.html</t>
         </is>
       </c>
     </row>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q226-sidebar-content-grid-grid-intermediate-challenge-226.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q226-sidebar-content-grid-grid-intermediate-challenge-226.html</t>
         </is>
       </c>
     </row>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q227-blog-highlight-grid-grid-intermediate-challenge-227.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q227-blog-highlight-grid-grid-intermediate-challenge-227.html</t>
         </is>
       </c>
     </row>
@@ -25360,7 +25360,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q228-stats-and-table-grid-grid-intermediate-challenge-228.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q228-stats-and-table-grid-grid-intermediate-challenge-228.html</t>
         </is>
       </c>
     </row>
@@ -25407,7 +25407,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q229-widget-control-board-grid-grid-intermediate-challenge-229.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q229-widget-control-board-grid-grid-intermediate-challenge-229.html</t>
         </is>
       </c>
     </row>
@@ -25454,7 +25454,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q230-research-summary-grid-grid-intermediate-challenge-230.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q230-research-summary-grid-grid-intermediate-challenge-230.html</t>
         </is>
       </c>
     </row>
@@ -25501,7 +25501,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q231-image-gallery-proportion-grid-grid-intermediate-challenge-231.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q231-image-gallery-proportion-grid-grid-intermediate-challenge-231.html</t>
         </is>
       </c>
     </row>
@@ -25548,7 +25548,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q232-landing-feature-grid-grid-intermediate-challenge-232.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q232-landing-feature-grid-grid-intermediate-challenge-232.html</t>
         </is>
       </c>
     </row>
@@ -25595,7 +25595,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q233-operations-control-grid-grid-intermediate-challenge-233.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q233-operations-control-grid-grid-intermediate-challenge-233.html</t>
         </is>
       </c>
     </row>
@@ -25642,7 +25642,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q234-department-overview-grid-grid-intermediate-challenge-234.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q234-department-overview-grid-grid-intermediate-challenge-234.html</t>
         </is>
       </c>
     </row>
@@ -25689,7 +25689,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q235-schedule-planner-grid-grid-intermediate-challenge-235.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q235-schedule-planner-grid-grid-intermediate-challenge-235.html</t>
         </is>
       </c>
     </row>
@@ -25736,7 +25736,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q236-offer-comparison-grid-grid-intermediate-challenge-236.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q236-offer-comparison-grid-grid-intermediate-challenge-236.html</t>
         </is>
       </c>
     </row>
@@ -25783,7 +25783,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q237-marketplace-listing-grid-grid-intermediate-challenge-237.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q237-marketplace-listing-grid-grid-intermediate-challenge-237.html</t>
         </is>
       </c>
     </row>
@@ -25830,7 +25830,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q238-campaign-results-grid-grid-intermediate-challenge-238.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q238-campaign-results-grid-grid-intermediate-challenge-238.html</t>
         </is>
       </c>
     </row>
@@ -25877,7 +25877,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q239-onboarding-steps-grid-grid-intermediate-challenge-239.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q239-onboarding-steps-grid-grid-intermediate-challenge-239.html</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/grid/q240-multi-panel-knowledge-grid-grid-intermediate-challenge-240.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/grid/q240-multi-panel-knowledge-grid-grid-intermediate-challenge-240.html</t>
         </is>
       </c>
     </row>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q241-breakpoint-driven-nav-shift-media-queries-intermediate-challenge-241.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q241-breakpoint-driven-nav-shift-media-queries-intermediate-challenge-241.html</t>
         </is>
       </c>
     </row>
@@ -26018,7 +26018,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q242-tablet-card-reflow-media-queries-intermediate-challenge-242.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q242-tablet-card-reflow-media-queries-intermediate-challenge-242.html</t>
         </is>
       </c>
     </row>
@@ -26065,7 +26065,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q243-desktop-typography-expansion-media-queries-intermediate-challenge-243.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q243-desktop-typography-expansion-media-queries-intermediate-challenge-243.html</t>
         </is>
       </c>
     </row>
@@ -26112,7 +26112,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q244-form-stack-conversion-media-queries-intermediate-challenge-244.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q244-form-stack-conversion-media-queries-intermediate-challenge-244.html</t>
         </is>
       </c>
     </row>
@@ -26159,7 +26159,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q245-sidebar-collapse-trigger-media-queries-intermediate-challenge-245.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q245-sidebar-collapse-trigger-media-queries-intermediate-challenge-245.html</t>
         </is>
       </c>
     </row>
@@ -26206,7 +26206,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q246-hero-proportion-change-media-queries-intermediate-challenge-246.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q246-hero-proportion-change-media-queries-intermediate-challenge-246.html</t>
         </is>
       </c>
     </row>
@@ -26253,7 +26253,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q247-button-group-wrapping-media-queries-intermediate-challenge-247.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q247-button-group-wrapping-media-queries-intermediate-challenge-247.html</t>
         </is>
       </c>
     </row>
@@ -26300,7 +26300,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q248-table-to-card-adaptation-media-queries-intermediate-challenge-248.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q248-table-to-card-adaptation-media-queries-intermediate-challenge-248.html</t>
         </is>
       </c>
     </row>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q249-gallery-column-reduction-media-queries-intermediate-challenge-249.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q249-gallery-column-reduction-media-queries-intermediate-challenge-249.html</t>
         </is>
       </c>
     </row>
@@ -26394,7 +26394,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q250-footer-stack-breakpoint-media-queries-intermediate-challenge-250.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q250-footer-stack-breakpoint-media-queries-intermediate-challenge-250.html</t>
         </is>
       </c>
     </row>
@@ -26441,7 +26441,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q251-sticky-header-enable-rule-media-queries-intermediate-challenge-251.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q251-sticky-header-enable-rule-media-queries-intermediate-challenge-251.html</t>
         </is>
       </c>
     </row>
@@ -26488,7 +26488,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q252-section-spacing-adaptation-media-queries-intermediate-challenge-252.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q252-section-spacing-adaptation-media-queries-intermediate-challenge-252.html</t>
         </is>
       </c>
     </row>
@@ -26535,7 +26535,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q253-banner-height-tuning-media-queries-intermediate-challenge-253.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q253-banner-height-tuning-media-queries-intermediate-challenge-253.html</t>
         </is>
       </c>
     </row>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q254-cta-position-switch-media-queries-intermediate-challenge-254.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q254-cta-position-switch-media-queries-intermediate-challenge-254.html</t>
         </is>
       </c>
     </row>
@@ -26629,7 +26629,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q255-grid-area-remap-media-queries-intermediate-challenge-255.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q255-grid-area-remap-media-queries-intermediate-challenge-255.html</t>
         </is>
       </c>
     </row>
@@ -26676,7 +26676,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q256-image-treatment-by-viewport-media-queries-intermediate-challenge-256.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q256-image-treatment-by-viewport-media-queries-intermediate-challenge-256.html</t>
         </is>
       </c>
     </row>
@@ -26723,7 +26723,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q257-input-width-adaptation-media-queries-intermediate-challenge-257.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q257-input-width-adaptation-media-queries-intermediate-challenge-257.html</t>
         </is>
       </c>
     </row>
@@ -26770,7 +26770,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q258-pricing-row-reorder-media-queries-intermediate-challenge-258.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q258-pricing-row-reorder-media-queries-intermediate-challenge-258.html</t>
         </is>
       </c>
     </row>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q259-visibility-toggle-by-width-media-queries-intermediate-challenge-259.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q259-visibility-toggle-by-width-media-queries-intermediate-challenge-259.html</t>
         </is>
       </c>
     </row>
@@ -26864,7 +26864,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q260-dashboard-block-shift-media-queries-intermediate-challenge-260.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q260-dashboard-block-shift-media-queries-intermediate-challenge-260.html</t>
         </is>
       </c>
     </row>
@@ -26911,7 +26911,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q261-two-pane-to-single-pane-media-queries-intermediate-challenge-261.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q261-two-pane-to-single-pane-media-queries-intermediate-challenge-261.html</t>
         </is>
       </c>
     </row>
@@ -26958,7 +26958,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q262-list-density-adaptation-media-queries-intermediate-challenge-262.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q262-list-density-adaptation-media-queries-intermediate-challenge-262.html</t>
         </is>
       </c>
     </row>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q263-metric-card-rearrangement-media-queries-intermediate-challenge-263.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q263-metric-card-rearrangement-media-queries-intermediate-challenge-263.html</t>
         </is>
       </c>
     </row>
@@ -27052,7 +27052,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q264-timeline-simplification-rule-media-queries-intermediate-challenge-264.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q264-timeline-simplification-rule-media-queries-intermediate-challenge-264.html</t>
         </is>
       </c>
     </row>
@@ -27099,7 +27099,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q265-control-panel-collapse-media-queries-intermediate-challenge-265.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q265-control-panel-collapse-media-queries-intermediate-challenge-265.html</t>
         </is>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q266-search-result-layout-flip-media-queries-intermediate-challenge-266.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q266-search-result-layout-flip-media-queries-intermediate-challenge-266.html</t>
         </is>
       </c>
     </row>
@@ -27193,7 +27193,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q267-feature-tiles-rebalance-media-queries-intermediate-challenge-267.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q267-feature-tiles-rebalance-media-queries-intermediate-challenge-267.html</t>
         </is>
       </c>
     </row>
@@ -27240,7 +27240,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q268-promo-copy-scaling-media-queries-intermediate-challenge-268.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q268-promo-copy-scaling-media-queries-intermediate-challenge-268.html</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q269-navigation-hit-area-adjustment-media-queries-intermediate-challenge-269.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q269-navigation-hit-area-adjustment-media-queries-intermediate-challenge-269.html</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/media-queries/q270-mobile-first-layering-conversion-media-queries-intermediate-challenge-270.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/media-queries/q270-mobile-first-layering-conversion-media-queries-intermediate-challenge-270.html</t>
         </is>
       </c>
     </row>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q271-saas-landing-multi-device-build-responsive-design-intermediate-challenge-271.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q271-saas-landing-multi-device-build-responsive-design-intermediate-challenge-271.html</t>
         </is>
       </c>
     </row>
@@ -27428,7 +27428,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q272-education-portal-adaptive-layout-responsive-design-intermediate-challenge-272.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q272-education-portal-adaptive-layout-responsive-design-intermediate-challenge-272.html</t>
         </is>
       </c>
     </row>
@@ -27475,7 +27475,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q273-clinic-website-fluid-flow-responsive-design-intermediate-challenge-273.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q273-clinic-website-fluid-flow-responsive-design-intermediate-challenge-273.html</t>
         </is>
       </c>
     </row>
@@ -27522,7 +27522,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-intermediate-challenge-274.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-intermediate-challenge-274.html</t>
         </is>
       </c>
     </row>
@@ -27569,7 +27569,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q275-travel-guide-responsive-build-responsive-design-intermediate-challenge-275.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q275-travel-guide-responsive-build-responsive-design-intermediate-challenge-275.html</t>
         </is>
       </c>
     </row>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q276-portfolio-site-fluid-components-responsive-design-intermediate-challenge-276.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q276-portfolio-site-fluid-components-responsive-design-intermediate-challenge-276.html</t>
         </is>
       </c>
     </row>
@@ -27663,7 +27663,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q277-community-platform-adaptive-shell-responsive-design-intermediate-challenge-277.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q277-community-platform-adaptive-shell-responsive-design-intermediate-challenge-277.html</t>
         </is>
       </c>
     </row>
@@ -27710,7 +27710,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q278-event-website-responsive-frame-responsive-design-intermediate-challenge-278.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q278-event-website-responsive-frame-responsive-design-intermediate-challenge-278.html</t>
         </is>
       </c>
     </row>
@@ -27757,7 +27757,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-intermediate-challenge-279.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-intermediate-challenge-279.html</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-intermediate-challenge-280.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-intermediate-challenge-280.html</t>
         </is>
       </c>
     </row>
@@ -27851,7 +27851,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q281-dashboard-adaptive-overview-responsive-design-intermediate-challenge-281.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q281-dashboard-adaptive-overview-responsive-design-intermediate-challenge-281.html</t>
         </is>
       </c>
     </row>
@@ -27898,7 +27898,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q282-booking-interface-responsive-build-responsive-design-intermediate-challenge-282.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q282-booking-interface-responsive-build-responsive-design-intermediate-challenge-282.html</t>
         </is>
       </c>
     </row>
@@ -27945,7 +27945,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-intermediate-challenge-283.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-intermediate-challenge-283.html</t>
         </is>
       </c>
     </row>
@@ -27992,7 +27992,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-intermediate-challenge-284.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-intermediate-challenge-284.html</t>
         </is>
       </c>
     </row>
@@ -28039,7 +28039,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-intermediate-challenge-285.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-intermediate-challenge-285.html</t>
         </is>
       </c>
     </row>
@@ -28086,7 +28086,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q286-help-center-responsive-structure-responsive-design-intermediate-challenge-286.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q286-help-center-responsive-structure-responsive-design-intermediate-challenge-286.html</t>
         </is>
       </c>
     </row>
@@ -28133,7 +28133,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-intermediate-challenge-287.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-intermediate-challenge-287.html</t>
         </is>
       </c>
     </row>
@@ -28180,7 +28180,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q288-course-platform-responsive-cards-responsive-design-intermediate-challenge-288.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q288-course-platform-responsive-cards-responsive-design-intermediate-challenge-288.html</t>
         </is>
       </c>
     </row>
@@ -28227,7 +28227,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q289-music-festival-adaptive-layout-responsive-design-intermediate-challenge-289.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q289-music-festival-adaptive-layout-responsive-design-intermediate-challenge-289.html</t>
         </is>
       </c>
     </row>
@@ -28274,7 +28274,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q290-research-portal-responsive-build-responsive-design-intermediate-challenge-290.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q290-research-portal-responsive-build-responsive-design-intermediate-challenge-290.html</t>
         </is>
       </c>
     </row>
@@ -28321,7 +28321,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-intermediate-challenge-291.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-intermediate-challenge-291.html</t>
         </is>
       </c>
     </row>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-intermediate-challenge-292.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-intermediate-challenge-292.html</t>
         </is>
       </c>
     </row>
@@ -28415,7 +28415,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q293-public-service-responsive-site-responsive-design-intermediate-challenge-293.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q293-public-service-responsive-site-responsive-design-intermediate-challenge-293.html</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-intermediate-challenge-294.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-intermediate-challenge-294.html</t>
         </is>
       </c>
     </row>
@@ -28509,7 +28509,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-intermediate-challenge-295.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-intermediate-challenge-295.html</t>
         </is>
       </c>
     </row>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q296-movie-review-responsive-layout-responsive-design-intermediate-challenge-296.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q296-movie-review-responsive-layout-responsive-design-intermediate-challenge-296.html</t>
         </is>
       </c>
     </row>
@@ -28603,7 +28603,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q297-real-estate-adaptive-listing-responsive-design-intermediate-challenge-297.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q297-real-estate-adaptive-listing-responsive-design-intermediate-challenge-297.html</t>
         </is>
       </c>
     </row>
@@ -28650,7 +28650,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-intermediate-challenge-298.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-intermediate-challenge-298.html</t>
         </is>
       </c>
     </row>
@@ -28697,7 +28697,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q299-tourism-board-responsive-story-responsive-design-intermediate-challenge-299.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q299-tourism-board-responsive-story-responsive-design-intermediate-challenge-299.html</t>
         </is>
       </c>
     </row>
@@ -28744,7 +28744,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/intermediate/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-intermediate-challenge-300.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/intermediate/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-intermediate-challenge-300.html</t>
         </is>
       </c>
     </row>
@@ -28863,7 +28863,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q001-portfolio-hero-blueprint-html-hard-challenge-001.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q001-portfolio-hero-blueprint-html-hard-challenge-001.html</t>
         </is>
       </c>
     </row>
@@ -28910,7 +28910,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q002-campus-club-home-structure-html-hard-challenge-002.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q002-campus-club-home-structure-html-hard-challenge-002.html</t>
         </is>
       </c>
     </row>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q003-startup-about-storyline-html-hard-challenge-003.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q003-startup-about-storyline-html-hard-challenge-003.html</t>
         </is>
       </c>
     </row>
@@ -29004,7 +29004,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q004-travel-blog-intro-layout-html-hard-challenge-004.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q004-travel-blog-intro-layout-html-hard-challenge-004.html</t>
         </is>
       </c>
     </row>
@@ -29051,7 +29051,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q005-food-menu-showcase-page-html-hard-challenge-005.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q005-food-menu-showcase-page-html-hard-challenge-005.html</t>
         </is>
       </c>
     </row>
@@ -29098,7 +29098,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q006-course-finder-landing-outline-html-hard-challenge-006.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q006-course-finder-landing-outline-html-hard-challenge-006.html</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q007-ngo-mission-page-structure-html-hard-challenge-007.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q007-ngo-mission-page-structure-html-hard-challenge-007.html</t>
         </is>
       </c>
     </row>
@@ -29192,7 +29192,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q008-podcast-episode-landing-html-hard-challenge-008.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q008-podcast-episode-landing-html-hard-challenge-008.html</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q009-fitness-coach-intro-page-html-hard-challenge-009.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q009-fitness-coach-intro-page-html-hard-challenge-009.html</t>
         </is>
       </c>
     </row>
@@ -29286,7 +29286,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q010-bookstore-discover-page-html-hard-challenge-010.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q010-bookstore-discover-page-html-hard-challenge-010.html</t>
         </is>
       </c>
     </row>
@@ -29333,7 +29333,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q011-event-countdown-content-page-html-hard-challenge-011.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q011-event-countdown-content-page-html-hard-challenge-011.html</t>
         </is>
       </c>
     </row>
@@ -29380,7 +29380,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q012-freelancer-service-page-skeleton-html-hard-challenge-012.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q012-freelancer-service-page-skeleton-html-hard-challenge-012.html</t>
         </is>
       </c>
     </row>
@@ -29427,7 +29427,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q013-museum-exhibit-intro-page-html-hard-challenge-013.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q013-museum-exhibit-intro-page-html-hard-challenge-013.html</t>
         </is>
       </c>
     </row>
@@ -29474,7 +29474,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q014-career-fair-info-page-html-hard-challenge-014.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q014-career-fair-info-page-html-hard-challenge-014.html</t>
         </is>
       </c>
     </row>
@@ -29521,7 +29521,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q015-tech-meetup-announcement-page-html-hard-challenge-015.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q015-tech-meetup-announcement-page-html-hard-challenge-015.html</t>
         </is>
       </c>
     </row>
@@ -29568,7 +29568,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q016-local-news-digest-home-html-hard-challenge-016.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q016-local-news-digest-home-html-hard-challenge-016.html</t>
         </is>
       </c>
     </row>
@@ -29615,7 +29615,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q017-recipe-discovery-landing-html-hard-challenge-017.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q017-recipe-discovery-landing-html-hard-challenge-017.html</t>
         </is>
       </c>
     </row>
@@ -29662,7 +29662,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q018-product-launch-intro-page-html-hard-challenge-018.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q018-product-launch-intro-page-html-hard-challenge-018.html</t>
         </is>
       </c>
     </row>
@@ -29709,7 +29709,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q019-student-project-gallery-page-html-hard-challenge-019.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q019-student-project-gallery-page-html-hard-challenge-019.html</t>
         </is>
       </c>
     </row>
@@ -29756,7 +29756,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q020-volunteer-drive-landing-html-hard-challenge-020.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q020-volunteer-drive-landing-html-hard-challenge-020.html</t>
         </is>
       </c>
     </row>
@@ -29803,7 +29803,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q021-language-learning-home-html-hard-challenge-021.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q021-language-learning-home-html-hard-challenge-021.html</t>
         </is>
       </c>
     </row>
@@ -29850,7 +29850,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q022-internship-portal-intro-html-hard-challenge-022.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q022-internship-portal-intro-html-hard-challenge-022.html</t>
         </is>
       </c>
     </row>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q023-healthcare-awareness-page-html-hard-challenge-023.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q023-healthcare-awareness-page-html-hard-challenge-023.html</t>
         </is>
       </c>
     </row>
@@ -29944,7 +29944,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q024-photography-journey-page-html-hard-challenge-024.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q024-photography-journey-page-html-hard-challenge-024.html</t>
         </is>
       </c>
     </row>
@@ -29991,7 +29991,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q025-coding-bootcamp-info-page-html-hard-challenge-025.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q025-coding-bootcamp-info-page-html-hard-challenge-025.html</t>
         </is>
       </c>
     </row>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q026-town-hall-notice-page-html-hard-challenge-026.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q026-town-hall-notice-page-html-hard-challenge-026.html</t>
         </is>
       </c>
     </row>
@@ -30085,7 +30085,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q027-scholarship-program-intro-html-hard-challenge-027.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q027-scholarship-program-intro-html-hard-challenge-027.html</t>
         </is>
       </c>
     </row>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q028-music-festival-welcome-page-html-hard-challenge-028.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q028-music-festival-welcome-page-html-hard-challenge-028.html</t>
         </is>
       </c>
     </row>
@@ -30179,7 +30179,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q029-real-estate-listing-intro-html-hard-challenge-029.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q029-real-estate-listing-intro-html-hard-challenge-029.html</t>
         </is>
       </c>
     </row>
@@ -30226,7 +30226,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/html/q030-climate-action-campaign-page-html-hard-challenge-030.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/html/q030-climate-action-campaign-page-html-hard-challenge-030.html</t>
         </is>
       </c>
     </row>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q031-accessible-editorial-article-semantic-html-hard-challenge-031.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q031-accessible-editorial-article-semantic-html-hard-challenge-031.html</t>
         </is>
       </c>
     </row>
@@ -30320,7 +30320,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q032-landmark-rich-government-notice-semantic-html-hard-challenge-032.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q032-landmark-rich-government-notice-semantic-html-hard-challenge-032.html</t>
         </is>
       </c>
     </row>
@@ -30367,7 +30367,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q033-research-summary-with-sections-semantic-html-hard-challenge-033.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q033-research-summary-with-sections-semantic-html-hard-challenge-033.html</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q034-open-source-release-notes-semantic-html-hard-challenge-034.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q034-open-source-release-notes-semantic-html-hard-challenge-034.html</t>
         </is>
       </c>
     </row>
@@ -30461,7 +30461,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q035-health-advisory-bulletin-semantic-html-hard-challenge-035.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q035-health-advisory-bulletin-semantic-html-hard-challenge-035.html</t>
         </is>
       </c>
     </row>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q036-newsroom-feature-with-asides-semantic-html-hard-challenge-036.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q036-newsroom-feature-with-asides-semantic-html-hard-challenge-036.html</t>
         </is>
       </c>
     </row>
@@ -30555,7 +30555,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q037-education-policy-explainer-semantic-html-hard-challenge-037.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q037-education-policy-explainer-semantic-html-hard-challenge-037.html</t>
         </is>
       </c>
     </row>
@@ -30602,7 +30602,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q038-product-case-study-narrative-semantic-html-hard-challenge-038.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q038-product-case-study-narrative-semantic-html-hard-challenge-038.html</t>
         </is>
       </c>
     </row>
@@ -30649,7 +30649,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q039-conference-report-with-time-data-semantic-html-hard-challenge-039.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q039-conference-report-with-time-data-semantic-html-hard-challenge-039.html</t>
         </is>
       </c>
     </row>
@@ -30696,7 +30696,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q040-community-program-digest-semantic-html-hard-challenge-040.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q040-community-program-digest-semantic-html-hard-challenge-040.html</t>
         </is>
       </c>
     </row>
@@ -30743,7 +30743,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q041-public-service-announcement-semantic-html-hard-challenge-041.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q041-public-service-announcement-semantic-html-hard-challenge-041.html</t>
         </is>
       </c>
     </row>
@@ -30790,7 +30790,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q042-digital-magazine-story-flow-semantic-html-hard-challenge-042.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q042-digital-magazine-story-flow-semantic-html-hard-challenge-042.html</t>
         </is>
       </c>
     </row>
@@ -30837,7 +30837,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q043-cinema-review-with-metadata-semantic-html-hard-challenge-043.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q043-cinema-review-with-metadata-semantic-html-hard-challenge-043.html</t>
         </is>
       </c>
     </row>
@@ -30884,7 +30884,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q044-travel-guide-with-highlights-semantic-html-hard-challenge-044.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q044-travel-guide-with-highlights-semantic-html-hard-challenge-044.html</t>
         </is>
       </c>
     </row>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q045-charity-report-with-figures-semantic-html-hard-challenge-045.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q045-charity-report-with-figures-semantic-html-hard-challenge-045.html</t>
         </is>
       </c>
     </row>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q046-startup-milestone-chronicle-semantic-html-hard-challenge-046.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q046-startup-milestone-chronicle-semantic-html-hard-challenge-046.html</t>
         </is>
       </c>
     </row>
@@ -31025,7 +31025,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q047-interview-transcript-publication-semantic-html-hard-challenge-047.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q047-interview-transcript-publication-semantic-html-hard-challenge-047.html</t>
         </is>
       </c>
     </row>
@@ -31072,7 +31072,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q048-workshop-recap-article-semantic-html-hard-challenge-048.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q048-workshop-recap-article-semantic-html-hard-challenge-048.html</t>
         </is>
       </c>
     </row>
@@ -31119,7 +31119,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q049-museum-research-abstract-semantic-html-hard-challenge-049.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q049-museum-research-abstract-semantic-html-hard-challenge-049.html</t>
         </is>
       </c>
     </row>
@@ -31166,7 +31166,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q050-environment-briefing-story-semantic-html-hard-challenge-050.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q050-environment-briefing-story-semantic-html-hard-challenge-050.html</t>
         </is>
       </c>
     </row>
@@ -31213,7 +31213,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q051-tech-standards-overview-semantic-html-hard-challenge-051.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q051-tech-standards-overview-semantic-html-hard-challenge-051.html</t>
         </is>
       </c>
     </row>
@@ -31260,7 +31260,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q052-library-initiative-report-semantic-html-hard-challenge-052.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q052-library-initiative-report-semantic-html-hard-challenge-052.html</t>
         </is>
       </c>
     </row>
@@ -31307,7 +31307,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q053-civic-update-thread-semantic-html-hard-challenge-053.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q053-civic-update-thread-semantic-html-hard-challenge-053.html</t>
         </is>
       </c>
     </row>
@@ -31354,7 +31354,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q054-agriculture-innovation-report-semantic-html-hard-challenge-054.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q054-agriculture-innovation-report-semantic-html-hard-challenge-054.html</t>
         </is>
       </c>
     </row>
@@ -31401,7 +31401,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q055-sports-analysis-editorial-semantic-html-hard-challenge-055.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q055-sports-analysis-editorial-semantic-html-hard-challenge-055.html</t>
         </is>
       </c>
     </row>
@@ -31448,7 +31448,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q056-cultural-festival-article-semantic-html-hard-challenge-056.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q056-cultural-festival-article-semantic-html-hard-challenge-056.html</t>
         </is>
       </c>
     </row>
@@ -31495,7 +31495,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q057-medical-procedure-overview-semantic-html-hard-challenge-057.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q057-medical-procedure-overview-semantic-html-hard-challenge-057.html</t>
         </is>
       </c>
     </row>
@@ -31542,7 +31542,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q058-urban-planning-update-semantic-html-hard-challenge-058.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q058-urban-planning-update-semantic-html-hard-challenge-058.html</t>
         </is>
       </c>
     </row>
@@ -31589,7 +31589,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q059-learning-roadmap-narrative-semantic-html-hard-challenge-059.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q059-learning-roadmap-narrative-semantic-html-hard-challenge-059.html</t>
         </is>
       </c>
     </row>
@@ -31636,7 +31636,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/semantic-html/q060-cybersecurity-incident-summary-semantic-html-hard-challenge-060.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/semantic-html/q060-cybersecurity-incident-summary-semantic-html-hard-challenge-060.html</t>
         </is>
       </c>
     </row>
@@ -31683,7 +31683,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q061-university-admission-application-forms-hard-challenge-061.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q061-university-admission-application-forms-hard-challenge-061.html</t>
         </is>
       </c>
     </row>
@@ -31730,7 +31730,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q062-job-referral-submission-forms-hard-challenge-062.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q062-job-referral-submission-forms-hard-challenge-062.html</t>
         </is>
       </c>
     </row>
@@ -31777,7 +31777,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q063-hospital-appointment-intake-forms-hard-challenge-063.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q063-hospital-appointment-intake-forms-hard-challenge-063.html</t>
         </is>
       </c>
     </row>
@@ -31824,7 +31824,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q064-vacation-leave-request-forms-hard-challenge-064.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q064-vacation-leave-request-forms-hard-challenge-064.html</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q065-freelance-project-brief-forms-hard-challenge-065.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q065-freelance-project-brief-forms-hard-challenge-065.html</t>
         </is>
       </c>
     </row>
@@ -31918,7 +31918,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q066-startup-demo-registration-forms-hard-challenge-066.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q066-startup-demo-registration-forms-hard-challenge-066.html</t>
         </is>
       </c>
     </row>
@@ -31965,7 +31965,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q067-scholarship-candidate-form-forms-hard-challenge-067.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q067-scholarship-candidate-form-forms-hard-challenge-067.html</t>
         </is>
       </c>
     </row>
@@ -32012,7 +32012,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q068-event-speaker-application-forms-hard-challenge-068.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q068-event-speaker-application-forms-hard-challenge-068.html</t>
         </is>
       </c>
     </row>
@@ -32059,7 +32059,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q069-customer-complaint-intake-forms-hard-challenge-069.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q069-customer-complaint-intake-forms-hard-challenge-069.html</t>
         </is>
       </c>
     </row>
@@ -32106,7 +32106,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q070-subscription-upgrade-request-forms-hard-challenge-070.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q070-subscription-upgrade-request-forms-hard-challenge-070.html</t>
         </is>
       </c>
     </row>
@@ -32153,7 +32153,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q071-insurance-claim-entry-forms-hard-challenge-071.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q071-insurance-claim-entry-forms-hard-challenge-071.html</t>
         </is>
       </c>
     </row>
@@ -32200,7 +32200,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q072-conference-volunteer-signup-forms-hard-challenge-072.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q072-conference-volunteer-signup-forms-hard-challenge-072.html</t>
         </is>
       </c>
     </row>
@@ -32247,7 +32247,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q073-coaching-session-booking-forms-hard-challenge-073.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q073-coaching-session-booking-forms-hard-challenge-073.html</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q074-product-return-request-forms-hard-challenge-074.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q074-product-return-request-forms-hard-challenge-074.html</t>
         </is>
       </c>
     </row>
@@ -32341,7 +32341,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q075-partnership-proposal-form-forms-hard-challenge-075.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q075-partnership-proposal-form-forms-hard-challenge-075.html</t>
         </is>
       </c>
     </row>
@@ -32388,7 +32388,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q076-technical-support-escalation-forms-hard-challenge-076.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q076-technical-support-escalation-forms-hard-challenge-076.html</t>
         </is>
       </c>
     </row>
@@ -32435,7 +32435,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q077-hackathon-team-registration-forms-hard-challenge-077.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q077-hackathon-team-registration-forms-hard-challenge-077.html</t>
         </is>
       </c>
     </row>
@@ -32482,7 +32482,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q078-course-feedback-survey-forms-hard-challenge-078.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q078-course-feedback-survey-forms-hard-challenge-078.html</t>
         </is>
       </c>
     </row>
@@ -32529,7 +32529,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q079-housing-rental-inquiry-forms-hard-challenge-079.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q079-housing-rental-inquiry-forms-hard-challenge-079.html</t>
         </is>
       </c>
     </row>
@@ -32576,7 +32576,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q080-internship-daily-report-forms-hard-challenge-080.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q080-internship-daily-report-forms-hard-challenge-080.html</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q081-bank-kyc-update-form-forms-hard-challenge-081.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q081-bank-kyc-update-form-forms-hard-challenge-081.html</t>
         </is>
       </c>
     </row>
@@ -32670,7 +32670,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q082-restaurant-catering-inquiry-forms-hard-challenge-082.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q082-restaurant-catering-inquiry-forms-hard-challenge-082.html</t>
         </is>
       </c>
     </row>
@@ -32717,7 +32717,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q083-ngo-volunteer-onboarding-forms-hard-challenge-083.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q083-ngo-volunteer-onboarding-forms-hard-challenge-083.html</t>
         </is>
       </c>
     </row>
@@ -32764,7 +32764,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q084-workshop-attendance-confirmation-forms-hard-challenge-084.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q084-workshop-attendance-confirmation-forms-hard-challenge-084.html</t>
         </is>
       </c>
     </row>
@@ -32811,7 +32811,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q085-saas-trial-activation-forms-hard-challenge-085.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q085-saas-trial-activation-forms-hard-challenge-085.html</t>
         </is>
       </c>
     </row>
@@ -32858,7 +32858,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q086-school-parent-meeting-slot-forms-hard-challenge-086.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q086-school-parent-meeting-slot-forms-hard-challenge-086.html</t>
         </is>
       </c>
     </row>
@@ -32905,7 +32905,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q087-clinic-lab-test-booking-forms-hard-challenge-087.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q087-clinic-lab-test-booking-forms-hard-challenge-087.html</t>
         </is>
       </c>
     </row>
@@ -32952,7 +32952,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q088-mentor-mentee-match-form-forms-hard-challenge-088.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q088-mentor-mentee-match-form-forms-hard-challenge-088.html</t>
         </is>
       </c>
     </row>
@@ -32999,7 +32999,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q089-travel-reimbursement-claim-forms-hard-challenge-089.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q089-travel-reimbursement-claim-forms-hard-challenge-089.html</t>
         </is>
       </c>
     </row>
@@ -33046,7 +33046,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/forms/q090-research-participation-consent-forms-hard-challenge-090.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/forms/q090-research-participation-consent-forms-hard-challenge-090.html</t>
         </is>
       </c>
     </row>
@@ -33093,7 +33093,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q091-semester-grade-ledger-tables-hard-challenge-091.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q091-semester-grade-ledger-tables-hard-challenge-091.html</t>
         </is>
       </c>
     </row>
@@ -33140,7 +33140,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q092-warehouse-stock-matrix-tables-hard-challenge-092.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q092-warehouse-stock-matrix-tables-hard-challenge-092.html</t>
         </is>
       </c>
     </row>
@@ -33187,7 +33187,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q093-quarterly-sales-tracker-tables-hard-challenge-093.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q093-quarterly-sales-tracker-tables-hard-challenge-093.html</t>
         </is>
       </c>
     </row>
@@ -33234,7 +33234,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q094-hospital-shift-allocation-tables-hard-challenge-094.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q094-hospital-shift-allocation-tables-hard-challenge-094.html</t>
         </is>
       </c>
     </row>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q095-flight-departure-board-tables-hard-challenge-095.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q095-flight-departure-board-tables-hard-challenge-095.html</t>
         </is>
       </c>
     </row>
@@ -33328,7 +33328,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q096-retail-price-comparison-tables-hard-challenge-096.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q096-retail-price-comparison-tables-hard-challenge-096.html</t>
         </is>
       </c>
     </row>
@@ -33375,7 +33375,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q097-project-sprint-burndown-table-tables-hard-challenge-097.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q097-project-sprint-burndown-table-tables-hard-challenge-097.html</t>
         </is>
       </c>
     </row>
@@ -33422,7 +33422,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q098-support-sla-performance-tables-hard-challenge-098.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q098-support-sla-performance-tables-hard-challenge-098.html</t>
         </is>
       </c>
     </row>
@@ -33469,7 +33469,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q099-attendance-compliance-sheet-tables-hard-challenge-099.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q099-attendance-compliance-sheet-tables-hard-challenge-099.html</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33516,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q100-subscription-renewal-grid-tables-hard-challenge-100.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q100-subscription-renewal-grid-tables-hard-challenge-100.html</t>
         </is>
       </c>
     </row>
@@ -33563,7 +33563,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q101-website-conversion-report-tables-hard-challenge-101.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q101-website-conversion-report-tables-hard-challenge-101.html</t>
         </is>
       </c>
     </row>
@@ -33610,7 +33610,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q102-manufacturing-defect-log-tables-hard-challenge-102.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q102-manufacturing-defect-log-tables-hard-challenge-102.html</t>
         </is>
       </c>
     </row>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q103-supplier-delivery-tracker-tables-hard-challenge-103.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q103-supplier-delivery-tracker-tables-hard-challenge-103.html</t>
         </is>
       </c>
     </row>
@@ -33704,7 +33704,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q104-budget-vs-spend-summary-tables-hard-challenge-104.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q104-budget-vs-spend-summary-tables-hard-challenge-104.html</t>
         </is>
       </c>
     </row>
@@ -33751,7 +33751,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q105-exam-seating-allocation-tables-hard-challenge-105.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q105-exam-seating-allocation-tables-hard-challenge-105.html</t>
         </is>
       </c>
     </row>
@@ -33798,7 +33798,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q106-sports-tournament-ladder-tables-hard-challenge-106.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q106-sports-tournament-ladder-tables-hard-challenge-106.html</t>
         </is>
       </c>
     </row>
@@ -33845,7 +33845,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q107-library-book-circulation-tables-hard-challenge-107.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q107-library-book-circulation-tables-hard-challenge-107.html</t>
         </is>
       </c>
     </row>
@@ -33892,7 +33892,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q108-class-timetable-board-tables-hard-challenge-108.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q108-class-timetable-board-tables-hard-challenge-108.html</t>
         </is>
       </c>
     </row>
@@ -33939,7 +33939,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q109-payroll-summary-table-tables-hard-challenge-109.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q109-payroll-summary-table-tables-hard-challenge-109.html</t>
         </is>
       </c>
     </row>
@@ -33986,7 +33986,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q110-incident-response-timeline-tables-hard-challenge-110.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q110-incident-response-timeline-tables-hard-challenge-110.html</t>
         </is>
       </c>
     </row>
@@ -34033,7 +34033,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q111-utility-usage-dashboard-table-tables-hard-challenge-111.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q111-utility-usage-dashboard-table-tables-hard-challenge-111.html</t>
         </is>
       </c>
     </row>
@@ -34080,7 +34080,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q112-training-progress-matrix-tables-hard-challenge-112.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q112-training-progress-matrix-tables-hard-challenge-112.html</t>
         </is>
       </c>
     </row>
@@ -34127,7 +34127,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q113-marketing-campaign-metrics-tables-hard-challenge-113.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q113-marketing-campaign-metrics-tables-hard-challenge-113.html</t>
         </is>
       </c>
     </row>
@@ -34174,7 +34174,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q114-ecommerce-order-audit-tables-hard-challenge-114.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q114-ecommerce-order-audit-tables-hard-challenge-114.html</t>
         </is>
       </c>
     </row>
@@ -34221,7 +34221,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q115-research-experiment-log-tables-hard-challenge-115.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q115-research-experiment-log-tables-hard-challenge-115.html</t>
         </is>
       </c>
     </row>
@@ -34268,7 +34268,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q116-branch-wise-revenue-table-tables-hard-challenge-116.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q116-branch-wise-revenue-table-tables-hard-challenge-116.html</t>
         </is>
       </c>
     </row>
@@ -34315,7 +34315,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q117-farm-yield-comparison-tables-hard-challenge-117.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q117-farm-yield-comparison-tables-hard-challenge-117.html</t>
         </is>
       </c>
     </row>
@@ -34362,7 +34362,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q118-transport-route-timings-tables-hard-challenge-118.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q118-transport-route-timings-tables-hard-challenge-118.html</t>
         </is>
       </c>
     </row>
@@ -34409,7 +34409,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q119-helpdesk-resolution-table-tables-hard-challenge-119.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q119-helpdesk-resolution-table-tables-hard-challenge-119.html</t>
         </is>
       </c>
     </row>
@@ -34456,7 +34456,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/tables/q120-customer-nps-breakdown-tables-hard-challenge-120.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/tables/q120-customer-nps-breakdown-tables-hard-challenge-120.html</t>
         </is>
       </c>
     </row>
@@ -34503,7 +34503,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q121-hero-section-theme-build-css-hard-challenge-121.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q121-hero-section-theme-build-css-hard-challenge-121.html</t>
         </is>
       </c>
     </row>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q122-feature-strip-visual-design-css-hard-challenge-122.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q122-feature-strip-visual-design-css-hard-challenge-122.html</t>
         </is>
       </c>
     </row>
@@ -34597,7 +34597,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q123-announcement-banner-styling-css-hard-challenge-123.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q123-announcement-banner-styling-css-hard-challenge-123.html</t>
         </is>
       </c>
     </row>
@@ -34644,7 +34644,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q124-profile-card-identity-system-css-hard-challenge-124.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q124-profile-card-identity-system-css-hard-challenge-124.html</t>
         </is>
       </c>
     </row>
@@ -34691,7 +34691,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q125-navigation-skin-architecture-css-hard-challenge-125.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q125-navigation-skin-architecture-css-hard-challenge-125.html</t>
         </is>
       </c>
     </row>
@@ -34738,7 +34738,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q126-pricing-tile-skinning-css-hard-challenge-126.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q126-pricing-tile-skinning-css-hard-challenge-126.html</t>
         </is>
       </c>
     </row>
@@ -34785,7 +34785,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q127-dashboard-widget-aesthetics-css-hard-challenge-127.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q127-dashboard-widget-aesthetics-css-hard-challenge-127.html</t>
         </is>
       </c>
     </row>
@@ -34832,7 +34832,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q128-testimonial-emphasis-style-css-hard-challenge-128.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q128-testimonial-emphasis-style-css-hard-challenge-128.html</t>
         </is>
       </c>
     </row>
@@ -34879,7 +34879,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q129-alert-severity-theme-pack-css-hard-challenge-129.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q129-alert-severity-theme-pack-css-hard-challenge-129.html</t>
         </is>
       </c>
     </row>
@@ -34926,7 +34926,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q130-tag-system-color-language-css-hard-challenge-130.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q130-tag-system-color-language-css-hard-challenge-130.html</t>
         </is>
       </c>
     </row>
@@ -34973,7 +34973,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q131-timeline-accent-styling-css-hard-challenge-131.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q131-timeline-accent-styling-css-hard-challenge-131.html</t>
         </is>
       </c>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q132-footer-visual-hierarchy-css-hard-challenge-132.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q132-footer-visual-hierarchy-css-hard-challenge-132.html</t>
         </is>
       </c>
     </row>
@@ -35067,7 +35067,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q133-article-typography-refinement-css-hard-challenge-133.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q133-article-typography-refinement-css-hard-challenge-133.html</t>
         </is>
       </c>
     </row>
@@ -35114,7 +35114,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q134-search-panel-interface-look-css-hard-challenge-134.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q134-search-panel-interface-look-css-hard-challenge-134.html</t>
         </is>
       </c>
     </row>
@@ -35161,7 +35161,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q135-promo-block-contrast-styling-css-hard-challenge-135.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q135-promo-block-contrast-styling-css-hard-challenge-135.html</t>
         </is>
       </c>
     </row>
@@ -35208,7 +35208,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q136-cta-group-interaction-styling-css-hard-challenge-136.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q136-cta-group-interaction-styling-css-hard-challenge-136.html</t>
         </is>
       </c>
     </row>
@@ -35255,7 +35255,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q137-section-divider-language-css-hard-challenge-137.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q137-section-divider-language-css-hard-challenge-137.html</t>
         </is>
       </c>
     </row>
@@ -35302,7 +35302,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q138-stats-counter-appearance-css-hard-challenge-138.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q138-stats-counter-appearance-css-hard-challenge-138.html</t>
         </is>
       </c>
     </row>
@@ -35349,7 +35349,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q139-form-state-theme-rules-css-hard-challenge-139.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q139-form-state-theme-rules-css-hard-challenge-139.html</t>
         </is>
       </c>
     </row>
@@ -35396,7 +35396,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q140-sidebar-branding-styles-css-hard-challenge-140.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q140-sidebar-branding-styles-css-hard-challenge-140.html</t>
         </is>
       </c>
     </row>
@@ -35443,7 +35443,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q141-loading-block-visual-state-css-hard-challenge-141.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q141-loading-block-visual-state-css-hard-challenge-141.html</t>
         </is>
       </c>
     </row>
@@ -35490,7 +35490,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q142-notification-stack-styling-css-hard-challenge-142.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q142-notification-stack-styling-css-hard-challenge-142.html</t>
         </is>
       </c>
     </row>
@@ -35537,7 +35537,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q143-badge-priority-color-rules-css-hard-challenge-143.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q143-badge-priority-color-rules-css-hard-challenge-143.html</t>
         </is>
       </c>
     </row>
@@ -35584,7 +35584,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q144-panel-depth-treatment-css-hard-challenge-144.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q144-panel-depth-treatment-css-hard-challenge-144.html</t>
         </is>
       </c>
     </row>
@@ -35631,7 +35631,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q145-card-hover-atmosphere-css-hard-challenge-145.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q145-card-hover-atmosphere-css-hard-challenge-145.html</t>
         </is>
       </c>
     </row>
@@ -35678,7 +35678,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q146-tab-navigation-styling-css-hard-challenge-146.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q146-tab-navigation-styling-css-hard-challenge-146.html</t>
         </is>
       </c>
     </row>
@@ -35725,7 +35725,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q147-review-block-quote-styling-css-hard-challenge-147.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q147-review-block-quote-styling-css-hard-challenge-147.html</t>
         </is>
       </c>
     </row>
@@ -35772,7 +35772,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q148-utility-class-theme-set-css-hard-challenge-148.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q148-utility-class-theme-set-css-hard-challenge-148.html</t>
         </is>
       </c>
     </row>
@@ -35819,7 +35819,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q149-feature-comparison-emphasis-css-hard-challenge-149.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q149-feature-comparison-emphasis-css-hard-challenge-149.html</t>
         </is>
       </c>
     </row>
@@ -35866,7 +35866,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/css/q150-microcopy-tone-styling-css-hard-challenge-150.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/css/q150-microcopy-tone-styling-css-hard-challenge-150.html</t>
         </is>
       </c>
     </row>
@@ -35913,7 +35913,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q151-card-padding-calibration-box-model-hard-challenge-151.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q151-card-padding-calibration-box-model-hard-challenge-151.html</t>
         </is>
       </c>
     </row>
@@ -35960,7 +35960,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q152-panel-margin-rhythm-box-model-hard-challenge-152.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q152-panel-margin-rhythm-box-model-hard-challenge-152.html</t>
         </is>
       </c>
     </row>
@@ -36007,7 +36007,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q153-info-tile-border-discipline-box-model-hard-challenge-153.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q153-info-tile-border-discipline-box-model-hard-challenge-153.html</t>
         </is>
       </c>
     </row>
@@ -36054,7 +36054,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q154-content-column-width-control-box-model-hard-challenge-154.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q154-content-column-width-control-box-model-hard-challenge-154.html</t>
         </is>
       </c>
     </row>
@@ -36101,7 +36101,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q155-widget-spacing-consistency-box-model-hard-challenge-155.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q155-widget-spacing-consistency-box-model-hard-challenge-155.html</t>
         </is>
       </c>
     </row>
@@ -36148,7 +36148,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q156-form-field-internal-spacing-box-model-hard-challenge-156.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q156-form-field-internal-spacing-box-model-hard-challenge-156.html</t>
         </is>
       </c>
     </row>
@@ -36195,7 +36195,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q157-header-to-body-gap-control-box-model-hard-challenge-157.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q157-header-to-body-gap-control-box-model-hard-challenge-157.html</t>
         </is>
       </c>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q158-sidebar-item-box-sizing-box-model-hard-challenge-158.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q158-sidebar-item-box-sizing-box-model-hard-challenge-158.html</t>
         </is>
       </c>
     </row>
@@ -36289,7 +36289,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q159-modal-frame-boundary-setup-box-model-hard-challenge-159.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q159-modal-frame-boundary-setup-box-model-hard-challenge-159.html</t>
         </is>
       </c>
     </row>
@@ -36336,7 +36336,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q160-cta-block-breathing-space-box-model-hard-challenge-160.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q160-cta-block-breathing-space-box-model-hard-challenge-160.html</t>
         </is>
       </c>
     </row>
@@ -36383,7 +36383,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q161-list-row-compact-spacing-box-model-hard-challenge-161.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q161-list-row-compact-spacing-box-model-hard-challenge-161.html</t>
         </is>
       </c>
     </row>
@@ -36430,7 +36430,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q162-avatar-meta-box-framing-box-model-hard-challenge-162.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q162-avatar-meta-box-framing-box-model-hard-challenge-162.html</t>
         </is>
       </c>
     </row>
@@ -36477,7 +36477,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q163-stats-tile-edge-balance-box-model-hard-challenge-163.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q163-stats-tile-edge-balance-box-model-hard-challenge-163.html</t>
         </is>
       </c>
     </row>
@@ -36524,7 +36524,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q164-caption-wrapper-width-rules-box-model-hard-challenge-164.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q164-caption-wrapper-width-rules-box-model-hard-challenge-164.html</t>
         </is>
       </c>
     </row>
@@ -36571,7 +36571,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q165-toolbar-item-separation-box-model-hard-challenge-165.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q165-toolbar-item-separation-box-model-hard-challenge-165.html</t>
         </is>
       </c>
     </row>
@@ -36618,7 +36618,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q166-section-shell-spacing-scale-box-model-hard-challenge-166.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q166-section-shell-spacing-scale-box-model-hard-challenge-166.html</t>
         </is>
       </c>
     </row>
@@ -36665,7 +36665,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q167-promo-ribbon-box-balance-box-model-hard-challenge-167.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q167-promo-ribbon-box-balance-box-model-hard-challenge-167.html</t>
         </is>
       </c>
     </row>
@@ -36712,7 +36712,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q168-article-paragraph-width-guard-box-model-hard-challenge-168.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q168-article-paragraph-width-guard-box-model-hard-challenge-168.html</t>
         </is>
       </c>
     </row>
@@ -36759,7 +36759,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q169-table-cell-padding-policy-box-model-hard-challenge-169.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q169-table-cell-padding-policy-box-model-hard-challenge-169.html</t>
         </is>
       </c>
     </row>
@@ -36806,7 +36806,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q170-gallery-tile-box-balance-box-model-hard-challenge-170.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q170-gallery-tile-box-balance-box-model-hard-challenge-170.html</t>
         </is>
       </c>
     </row>
@@ -36853,7 +36853,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q171-notification-container-sizing-box-model-hard-challenge-171.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q171-notification-container-sizing-box-model-hard-challenge-171.html</t>
         </is>
       </c>
     </row>
@@ -36900,7 +36900,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q172-pricing-card-edge-rhythm-box-model-hard-challenge-172.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q172-pricing-card-edge-rhythm-box-model-hard-challenge-172.html</t>
         </is>
       </c>
     </row>
@@ -36947,7 +36947,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q173-faq-panel-spacing-logic-box-model-hard-challenge-173.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q173-faq-panel-spacing-logic-box-model-hard-challenge-173.html</t>
         </is>
       </c>
     </row>
@@ -36994,7 +36994,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q174-timeline-node-box-spacing-box-model-hard-challenge-174.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q174-timeline-node-box-spacing-box-model-hard-challenge-174.html</t>
         </is>
       </c>
     </row>
@@ -37041,7 +37041,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q175-action-bar-padding-grid-box-model-hard-challenge-175.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q175-action-bar-padding-grid-box-model-hard-challenge-175.html</t>
         </is>
       </c>
     </row>
@@ -37088,7 +37088,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q176-profile-summary-frame-box-model-hard-challenge-176.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q176-profile-summary-frame-box-model-hard-challenge-176.html</t>
         </is>
       </c>
     </row>
@@ -37135,7 +37135,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q177-comment-box-vertical-rhythm-box-model-hard-challenge-177.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q177-comment-box-vertical-rhythm-box-model-hard-challenge-177.html</t>
         </is>
       </c>
     </row>
@@ -37182,7 +37182,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q178-checkout-summary-boundaries-box-model-hard-challenge-178.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q178-checkout-summary-boundaries-box-model-hard-challenge-178.html</t>
         </is>
       </c>
     </row>
@@ -37229,7 +37229,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q179-card-stack-consistent-offsets-box-model-hard-challenge-179.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q179-card-stack-consistent-offsets-box-model-hard-challenge-179.html</t>
         </is>
       </c>
     </row>
@@ -37276,7 +37276,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/box-model/q180-footer-link-block-sizing-box-model-hard-challenge-180.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/box-model/q180-footer-link-block-sizing-box-model-hard-challenge-180.html</t>
         </is>
       </c>
     </row>
@@ -37323,7 +37323,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q181-top-nav-distribution-flexbox-hard-challenge-181.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q181-top-nav-distribution-flexbox-hard-challenge-181.html</t>
         </is>
       </c>
     </row>
@@ -37370,7 +37370,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q182-action-toolbar-alignment-flexbox-hard-challenge-182.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q182-action-toolbar-alignment-flexbox-hard-challenge-182.html</t>
         </is>
       </c>
     </row>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q183-profile-header-justification-flexbox-hard-challenge-183.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q183-profile-header-justification-flexbox-hard-challenge-183.html</t>
         </is>
       </c>
     </row>
@@ -37464,7 +37464,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q184-card-deck-wrapping-rules-flexbox-hard-challenge-184.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q184-card-deck-wrapping-rules-flexbox-hard-challenge-184.html</t>
         </is>
       </c>
     </row>
@@ -37511,7 +37511,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q185-pricing-row-equalization-flexbox-hard-challenge-185.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q185-pricing-row-equalization-flexbox-hard-challenge-185.html</t>
         </is>
       </c>
     </row>
@@ -37558,7 +37558,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q186-form-controls-inline-layout-flexbox-hard-challenge-186.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q186-form-controls-inline-layout-flexbox-hard-challenge-186.html</t>
         </is>
       </c>
     </row>
@@ -37605,7 +37605,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q187-comment-header-alignment-flexbox-hard-challenge-187.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q187-comment-header-alignment-flexbox-hard-challenge-187.html</t>
         </is>
       </c>
     </row>
@@ -37652,7 +37652,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q188-sidebar-menu-distribution-flexbox-hard-challenge-188.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q188-sidebar-menu-distribution-flexbox-hard-challenge-188.html</t>
         </is>
       </c>
     </row>
@@ -37699,7 +37699,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q189-mobile-header-flex-shift-flexbox-hard-challenge-189.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q189-mobile-header-flex-shift-flexbox-hard-challenge-189.html</t>
         </is>
       </c>
     </row>
@@ -37746,7 +37746,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q190-feature-split-justify-pattern-flexbox-hard-challenge-190.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q190-feature-split-justify-pattern-flexbox-hard-challenge-190.html</t>
         </is>
       </c>
     </row>
@@ -37793,7 +37793,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q191-rating-row-alignment-flexbox-hard-challenge-191.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q191-rating-row-alignment-flexbox-hard-challenge-191.html</t>
         </is>
       </c>
     </row>
@@ -37840,7 +37840,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q192-media-object-horizontal-flow-flexbox-hard-challenge-192.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q192-media-object-horizontal-flow-flexbox-hard-challenge-192.html</t>
         </is>
       </c>
     </row>
@@ -37887,7 +37887,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q193-tag-wrap-control-flexbox-hard-challenge-193.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q193-tag-wrap-control-flexbox-hard-challenge-193.html</t>
         </is>
       </c>
     </row>
@@ -37934,7 +37934,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q194-checkout-totals-alignment-flexbox-hard-challenge-194.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q194-checkout-totals-alignment-flexbox-hard-challenge-194.html</t>
         </is>
       </c>
     </row>
@@ -37981,7 +37981,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q195-icon-label-pairing-flexbox-hard-challenge-195.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q195-icon-label-pairing-flexbox-hard-challenge-195.html</t>
         </is>
       </c>
     </row>
@@ -38028,7 +38028,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q196-gallery-caption-balance-flexbox-hard-challenge-196.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q196-gallery-caption-balance-flexbox-hard-challenge-196.html</t>
         </is>
       </c>
     </row>
@@ -38075,7 +38075,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q197-task-item-alignment-flexbox-hard-challenge-197.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q197-task-item-alignment-flexbox-hard-challenge-197.html</t>
         </is>
       </c>
     </row>
@@ -38122,7 +38122,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q198-search-result-action-row-flexbox-hard-challenge-198.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q198-search-result-action-row-flexbox-hard-challenge-198.html</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38169,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q199-sticky-footer-link-alignment-flexbox-hard-challenge-199.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q199-sticky-footer-link-alignment-flexbox-hard-challenge-199.html</t>
         </is>
       </c>
     </row>
@@ -38216,7 +38216,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q200-kpi-row-distribution-flexbox-hard-challenge-200.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q200-kpi-row-distribution-flexbox-hard-challenge-200.html</t>
         </is>
       </c>
     </row>
@@ -38263,7 +38263,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q201-avatar-text-baseline-flexbox-hard-challenge-201.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q201-avatar-text-baseline-flexbox-hard-challenge-201.html</t>
         </is>
       </c>
     </row>
@@ -38310,7 +38310,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q202-button-cluster-wrap-strategy-flexbox-hard-challenge-202.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q202-button-cluster-wrap-strategy-flexbox-hard-challenge-202.html</t>
         </is>
       </c>
     </row>
@@ -38357,7 +38357,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q203-menu-toggle-spacing-flexbox-hard-challenge-203.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q203-menu-toggle-spacing-flexbox-hard-challenge-203.html</t>
         </is>
       </c>
     </row>
@@ -38404,7 +38404,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q204-notification-item-alignment-flexbox-hard-challenge-204.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q204-notification-item-alignment-flexbox-hard-challenge-204.html</t>
         </is>
       </c>
     </row>
@@ -38451,7 +38451,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q205-filter-bar-justify-rules-flexbox-hard-challenge-205.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q205-filter-bar-justify-rules-flexbox-hard-challenge-205.html</t>
         </is>
       </c>
     </row>
@@ -38498,7 +38498,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q206-timeline-row-distribution-flexbox-hard-challenge-206.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q206-timeline-row-distribution-flexbox-hard-challenge-206.html</t>
         </is>
       </c>
     </row>
@@ -38545,7 +38545,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q207-progress-card-content-flow-flexbox-hard-challenge-207.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q207-progress-card-content-flow-flexbox-hard-challenge-207.html</t>
         </is>
       </c>
     </row>
@@ -38592,7 +38592,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q208-list-item-meta-alignment-flexbox-hard-challenge-208.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q208-list-item-meta-alignment-flexbox-hard-challenge-208.html</t>
         </is>
       </c>
     </row>
@@ -38639,7 +38639,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q209-chat-bubble-row-layout-flexbox-hard-challenge-209.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q209-chat-bubble-row-layout-flexbox-hard-challenge-209.html</t>
         </is>
       </c>
     </row>
@@ -38686,7 +38686,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/flexbox/q210-hero-cta-group-alignment-flexbox-hard-challenge-210.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/flexbox/q210-hero-cta-group-alignment-flexbox-hard-challenge-210.html</t>
         </is>
       </c>
     </row>
@@ -38733,7 +38733,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q211-analytics-overview-lattice-grid-hard-challenge-211.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q211-analytics-overview-lattice-grid-hard-challenge-211.html</t>
         </is>
       </c>
     </row>
@@ -38780,7 +38780,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q212-course-catalog-grid-system-grid-hard-challenge-212.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q212-course-catalog-grid-system-grid-hard-challenge-212.html</t>
         </is>
       </c>
     </row>
@@ -38827,7 +38827,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q213-portfolio-mosaic-grid-grid-hard-challenge-213.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q213-portfolio-mosaic-grid-grid-hard-challenge-213.html</t>
         </is>
       </c>
     </row>
@@ -38874,7 +38874,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q214-product-shelf-grid-grid-hard-challenge-214.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q214-product-shelf-grid-grid-hard-challenge-214.html</t>
         </is>
       </c>
     </row>
@@ -38921,7 +38921,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q215-editorial-magazine-grid-grid-hard-challenge-215.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q215-editorial-magazine-grid-grid-hard-challenge-215.html</t>
         </is>
       </c>
     </row>
@@ -38968,7 +38968,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q216-admin-console-grid-grid-hard-challenge-216.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q216-admin-console-grid-grid-hard-challenge-216.html</t>
         </is>
       </c>
     </row>
@@ -39015,7 +39015,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q217-learning-module-matrix-grid-hard-challenge-217.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q217-learning-module-matrix-grid-hard-challenge-217.html</t>
         </is>
       </c>
     </row>
@@ -39062,7 +39062,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q218-kpi-snapshot-grid-grid-hard-challenge-218.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q218-kpi-snapshot-grid-grid-hard-challenge-218.html</t>
         </is>
       </c>
     </row>
@@ -39109,7 +39109,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q219-team-directory-mosaic-grid-hard-challenge-219.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q219-team-directory-mosaic-grid-hard-challenge-219.html</t>
         </is>
       </c>
     </row>
@@ -39156,7 +39156,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q220-news-digest-grid-frame-grid-hard-challenge-220.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q220-news-digest-grid-frame-grid-hard-challenge-220.html</t>
         </is>
       </c>
     </row>
@@ -39203,7 +39203,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q221-case-study-showcase-grid-grid-hard-challenge-221.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q221-case-study-showcase-grid-grid-hard-challenge-221.html</t>
         </is>
       </c>
     </row>
@@ -39250,7 +39250,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q222-calendar-planning-grid-grid-hard-challenge-222.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q222-calendar-planning-grid-grid-hard-challenge-222.html</t>
         </is>
       </c>
     </row>
@@ -39297,7 +39297,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q223-pricing-matrix-grid-grid-hard-challenge-223.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q223-pricing-matrix-grid-grid-hard-challenge-223.html</t>
         </is>
       </c>
     </row>
@@ -39344,7 +39344,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q224-service-card-grid-grid-hard-challenge-224.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q224-service-card-grid-grid-hard-challenge-224.html</t>
         </is>
       </c>
     </row>
@@ -39391,7 +39391,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q225-feature-matrix-alignment-grid-grid-hard-challenge-225.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q225-feature-matrix-alignment-grid-grid-hard-challenge-225.html</t>
         </is>
       </c>
     </row>
@@ -39438,7 +39438,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q226-sidebar-content-grid-grid-hard-challenge-226.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q226-sidebar-content-grid-grid-hard-challenge-226.html</t>
         </is>
       </c>
     </row>
@@ -39485,7 +39485,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q227-blog-highlight-grid-grid-hard-challenge-227.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q227-blog-highlight-grid-grid-hard-challenge-227.html</t>
         </is>
       </c>
     </row>
@@ -39532,7 +39532,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q228-stats-and-table-grid-grid-hard-challenge-228.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q228-stats-and-table-grid-grid-hard-challenge-228.html</t>
         </is>
       </c>
     </row>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q229-widget-control-board-grid-grid-hard-challenge-229.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q229-widget-control-board-grid-grid-hard-challenge-229.html</t>
         </is>
       </c>
     </row>
@@ -39626,7 +39626,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q230-research-summary-grid-grid-hard-challenge-230.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q230-research-summary-grid-grid-hard-challenge-230.html</t>
         </is>
       </c>
     </row>
@@ -39673,7 +39673,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q231-image-gallery-proportion-grid-grid-hard-challenge-231.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q231-image-gallery-proportion-grid-grid-hard-challenge-231.html</t>
         </is>
       </c>
     </row>
@@ -39720,7 +39720,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q232-landing-feature-grid-grid-hard-challenge-232.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q232-landing-feature-grid-grid-hard-challenge-232.html</t>
         </is>
       </c>
     </row>
@@ -39767,7 +39767,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q233-operations-control-grid-grid-hard-challenge-233.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q233-operations-control-grid-grid-hard-challenge-233.html</t>
         </is>
       </c>
     </row>
@@ -39814,7 +39814,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q234-department-overview-grid-grid-hard-challenge-234.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q234-department-overview-grid-grid-hard-challenge-234.html</t>
         </is>
       </c>
     </row>
@@ -39861,7 +39861,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q235-schedule-planner-grid-grid-hard-challenge-235.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q235-schedule-planner-grid-grid-hard-challenge-235.html</t>
         </is>
       </c>
     </row>
@@ -39908,7 +39908,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q236-offer-comparison-grid-grid-hard-challenge-236.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q236-offer-comparison-grid-grid-hard-challenge-236.html</t>
         </is>
       </c>
     </row>
@@ -39955,7 +39955,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q237-marketplace-listing-grid-grid-hard-challenge-237.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q237-marketplace-listing-grid-grid-hard-challenge-237.html</t>
         </is>
       </c>
     </row>
@@ -40002,7 +40002,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q238-campaign-results-grid-grid-hard-challenge-238.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q238-campaign-results-grid-grid-hard-challenge-238.html</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q239-onboarding-steps-grid-grid-hard-challenge-239.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q239-onboarding-steps-grid-grid-hard-challenge-239.html</t>
         </is>
       </c>
     </row>
@@ -40096,7 +40096,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/grid/q240-multi-panel-knowledge-grid-grid-hard-challenge-240.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/grid/q240-multi-panel-knowledge-grid-grid-hard-challenge-240.html</t>
         </is>
       </c>
     </row>
@@ -40143,7 +40143,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q241-breakpoint-driven-nav-shift-media-queries-hard-challenge-241.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q241-breakpoint-driven-nav-shift-media-queries-hard-challenge-241.html</t>
         </is>
       </c>
     </row>
@@ -40190,7 +40190,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q242-tablet-card-reflow-media-queries-hard-challenge-242.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q242-tablet-card-reflow-media-queries-hard-challenge-242.html</t>
         </is>
       </c>
     </row>
@@ -40237,7 +40237,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q243-desktop-typography-expansion-media-queries-hard-challenge-243.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q243-desktop-typography-expansion-media-queries-hard-challenge-243.html</t>
         </is>
       </c>
     </row>
@@ -40284,7 +40284,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q244-form-stack-conversion-media-queries-hard-challenge-244.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q244-form-stack-conversion-media-queries-hard-challenge-244.html</t>
         </is>
       </c>
     </row>
@@ -40331,7 +40331,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q245-sidebar-collapse-trigger-media-queries-hard-challenge-245.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q245-sidebar-collapse-trigger-media-queries-hard-challenge-245.html</t>
         </is>
       </c>
     </row>
@@ -40378,7 +40378,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q246-hero-proportion-change-media-queries-hard-challenge-246.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q246-hero-proportion-change-media-queries-hard-challenge-246.html</t>
         </is>
       </c>
     </row>
@@ -40425,7 +40425,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q247-button-group-wrapping-media-queries-hard-challenge-247.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q247-button-group-wrapping-media-queries-hard-challenge-247.html</t>
         </is>
       </c>
     </row>
@@ -40472,7 +40472,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q248-table-to-card-adaptation-media-queries-hard-challenge-248.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q248-table-to-card-adaptation-media-queries-hard-challenge-248.html</t>
         </is>
       </c>
     </row>
@@ -40519,7 +40519,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q249-gallery-column-reduction-media-queries-hard-challenge-249.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q249-gallery-column-reduction-media-queries-hard-challenge-249.html</t>
         </is>
       </c>
     </row>
@@ -40566,7 +40566,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q250-footer-stack-breakpoint-media-queries-hard-challenge-250.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q250-footer-stack-breakpoint-media-queries-hard-challenge-250.html</t>
         </is>
       </c>
     </row>
@@ -40613,7 +40613,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q251-sticky-header-enable-rule-media-queries-hard-challenge-251.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q251-sticky-header-enable-rule-media-queries-hard-challenge-251.html</t>
         </is>
       </c>
     </row>
@@ -40660,7 +40660,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q252-section-spacing-adaptation-media-queries-hard-challenge-252.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q252-section-spacing-adaptation-media-queries-hard-challenge-252.html</t>
         </is>
       </c>
     </row>
@@ -40707,7 +40707,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q253-banner-height-tuning-media-queries-hard-challenge-253.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q253-banner-height-tuning-media-queries-hard-challenge-253.html</t>
         </is>
       </c>
     </row>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q254-cta-position-switch-media-queries-hard-challenge-254.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q254-cta-position-switch-media-queries-hard-challenge-254.html</t>
         </is>
       </c>
     </row>
@@ -40801,7 +40801,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q255-grid-area-remap-media-queries-hard-challenge-255.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q255-grid-area-remap-media-queries-hard-challenge-255.html</t>
         </is>
       </c>
     </row>
@@ -40848,7 +40848,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q256-image-treatment-by-viewport-media-queries-hard-challenge-256.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q256-image-treatment-by-viewport-media-queries-hard-challenge-256.html</t>
         </is>
       </c>
     </row>
@@ -40895,7 +40895,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q257-input-width-adaptation-media-queries-hard-challenge-257.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q257-input-width-adaptation-media-queries-hard-challenge-257.html</t>
         </is>
       </c>
     </row>
@@ -40942,7 +40942,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q258-pricing-row-reorder-media-queries-hard-challenge-258.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q258-pricing-row-reorder-media-queries-hard-challenge-258.html</t>
         </is>
       </c>
     </row>
@@ -40989,7 +40989,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q259-visibility-toggle-by-width-media-queries-hard-challenge-259.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q259-visibility-toggle-by-width-media-queries-hard-challenge-259.html</t>
         </is>
       </c>
     </row>
@@ -41036,7 +41036,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q260-dashboard-block-shift-media-queries-hard-challenge-260.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q260-dashboard-block-shift-media-queries-hard-challenge-260.html</t>
         </is>
       </c>
     </row>
@@ -41083,7 +41083,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q261-two-pane-to-single-pane-media-queries-hard-challenge-261.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q261-two-pane-to-single-pane-media-queries-hard-challenge-261.html</t>
         </is>
       </c>
     </row>
@@ -41130,7 +41130,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q262-list-density-adaptation-media-queries-hard-challenge-262.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q262-list-density-adaptation-media-queries-hard-challenge-262.html</t>
         </is>
       </c>
     </row>
@@ -41177,7 +41177,7 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q263-metric-card-rearrangement-media-queries-hard-challenge-263.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q263-metric-card-rearrangement-media-queries-hard-challenge-263.html</t>
         </is>
       </c>
     </row>
@@ -41224,7 +41224,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q264-timeline-simplification-rule-media-queries-hard-challenge-264.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q264-timeline-simplification-rule-media-queries-hard-challenge-264.html</t>
         </is>
       </c>
     </row>
@@ -41271,7 +41271,7 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q265-control-panel-collapse-media-queries-hard-challenge-265.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q265-control-panel-collapse-media-queries-hard-challenge-265.html</t>
         </is>
       </c>
     </row>
@@ -41318,7 +41318,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q266-search-result-layout-flip-media-queries-hard-challenge-266.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q266-search-result-layout-flip-media-queries-hard-challenge-266.html</t>
         </is>
       </c>
     </row>
@@ -41365,7 +41365,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q267-feature-tiles-rebalance-media-queries-hard-challenge-267.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q267-feature-tiles-rebalance-media-queries-hard-challenge-267.html</t>
         </is>
       </c>
     </row>
@@ -41412,7 +41412,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q268-promo-copy-scaling-media-queries-hard-challenge-268.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q268-promo-copy-scaling-media-queries-hard-challenge-268.html</t>
         </is>
       </c>
     </row>
@@ -41459,7 +41459,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q269-navigation-hit-area-adjustment-media-queries-hard-challenge-269.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q269-navigation-hit-area-adjustment-media-queries-hard-challenge-269.html</t>
         </is>
       </c>
     </row>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/media-queries/q270-mobile-first-layering-conversion-media-queries-hard-challenge-270.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/media-queries/q270-mobile-first-layering-conversion-media-queries-hard-challenge-270.html</t>
         </is>
       </c>
     </row>
@@ -41553,7 +41553,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q271-saas-landing-multi-device-build-responsive-design-hard-challenge-271.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q271-saas-landing-multi-device-build-responsive-design-hard-challenge-271.html</t>
         </is>
       </c>
     </row>
@@ -41600,7 +41600,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q272-education-portal-adaptive-layout-responsive-design-hard-challenge-272.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q272-education-portal-adaptive-layout-responsive-design-hard-challenge-272.html</t>
         </is>
       </c>
     </row>
@@ -41647,7 +41647,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q273-clinic-website-fluid-flow-responsive-design-hard-challenge-273.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q273-clinic-website-fluid-flow-responsive-design-hard-challenge-273.html</t>
         </is>
       </c>
     </row>
@@ -41694,7 +41694,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-hard-challenge-274.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q274-restaurant-site-adaptive-home-responsive-design-hard-challenge-274.html</t>
         </is>
       </c>
     </row>
@@ -41741,7 +41741,7 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q275-travel-guide-responsive-build-responsive-design-hard-challenge-275.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q275-travel-guide-responsive-build-responsive-design-hard-challenge-275.html</t>
         </is>
       </c>
     </row>
@@ -41788,7 +41788,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q276-portfolio-site-fluid-components-responsive-design-hard-challenge-276.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q276-portfolio-site-fluid-components-responsive-design-hard-challenge-276.html</t>
         </is>
       </c>
     </row>
@@ -41835,7 +41835,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q277-community-platform-adaptive-shell-responsive-design-hard-challenge-277.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q277-community-platform-adaptive-shell-responsive-design-hard-challenge-277.html</t>
         </is>
       </c>
     </row>
@@ -41882,7 +41882,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q278-event-website-responsive-frame-responsive-design-hard-challenge-278.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q278-event-website-responsive-frame-responsive-design-hard-challenge-278.html</t>
         </is>
       </c>
     </row>
@@ -41929,7 +41929,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-hard-challenge-279.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q279-startup-marketing-adaptive-page-responsive-design-hard-challenge-279.html</t>
         </is>
       </c>
     </row>
@@ -41976,7 +41976,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-hard-challenge-280.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q280-news-hub-multi-breakpoint-design-responsive-design-hard-challenge-280.html</t>
         </is>
       </c>
     </row>
@@ -42023,7 +42023,7 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q281-dashboard-adaptive-overview-responsive-design-hard-challenge-281.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q281-dashboard-adaptive-overview-responsive-design-hard-challenge-281.html</t>
         </is>
       </c>
     </row>
@@ -42070,7 +42070,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q282-booking-interface-responsive-build-responsive-design-hard-challenge-282.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q282-booking-interface-responsive-build-responsive-design-hard-challenge-282.html</t>
         </is>
       </c>
     </row>
@@ -42117,7 +42117,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-hard-challenge-283.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q283-magazine-site-responsive-narrative-responsive-design-hard-challenge-283.html</t>
         </is>
       </c>
     </row>
@@ -42164,7 +42164,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-hard-challenge-284.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q284-ngo-campaign-responsive-page-responsive-design-hard-challenge-284.html</t>
         </is>
       </c>
     </row>
@@ -42211,7 +42211,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-hard-challenge-285.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q285-ecommerce-adaptive-catalog-responsive-design-hard-challenge-285.html</t>
         </is>
       </c>
     </row>
@@ -42258,7 +42258,7 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q286-help-center-responsive-structure-responsive-design-hard-challenge-286.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q286-help-center-responsive-structure-responsive-design-hard-challenge-286.html</t>
         </is>
       </c>
     </row>
@@ -42305,7 +42305,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-hard-challenge-287.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q287-developer-docs-adaptive-readability-responsive-design-hard-challenge-287.html</t>
         </is>
       </c>
     </row>
@@ -42352,7 +42352,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q288-course-platform-responsive-cards-responsive-design-hard-challenge-288.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q288-course-platform-responsive-cards-responsive-design-hard-challenge-288.html</t>
         </is>
       </c>
     </row>
@@ -42399,7 +42399,7 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q289-music-festival-adaptive-layout-responsive-design-hard-challenge-289.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q289-music-festival-adaptive-layout-responsive-design-hard-challenge-289.html</t>
         </is>
       </c>
     </row>
@@ -42446,7 +42446,7 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q290-research-portal-responsive-build-responsive-design-hard-challenge-290.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q290-research-portal-responsive-build-responsive-design-hard-challenge-290.html</t>
         </is>
       </c>
     </row>
@@ -42493,7 +42493,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-hard-challenge-291.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q291-banking-ui-adaptive-panel-responsive-design-hard-challenge-291.html</t>
         </is>
       </c>
     </row>
@@ -42540,7 +42540,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-hard-challenge-292.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q292-recruitment-portal-responsive-grid-responsive-design-hard-challenge-292.html</t>
         </is>
       </c>
     </row>
@@ -42587,7 +42587,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q293-public-service-responsive-site-responsive-design-hard-challenge-293.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q293-public-service-responsive-site-responsive-design-hard-challenge-293.html</t>
         </is>
       </c>
     </row>
@@ -42634,7 +42634,7 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-hard-challenge-294.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q294-fitness-program-adaptive-dashboard-responsive-design-hard-challenge-294.html</t>
         </is>
       </c>
     </row>
@@ -42681,7 +42681,7 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-hard-challenge-295.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q295-agriculture-insights-responsive-page-responsive-design-hard-challenge-295.html</t>
         </is>
       </c>
     </row>
@@ -42728,7 +42728,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q296-movie-review-responsive-layout-responsive-design-hard-challenge-296.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q296-movie-review-responsive-layout-responsive-design-hard-challenge-296.html</t>
         </is>
       </c>
     </row>
@@ -42775,7 +42775,7 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q297-real-estate-adaptive-listing-responsive-design-hard-challenge-297.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q297-real-estate-adaptive-listing-responsive-design-hard-challenge-297.html</t>
         </is>
       </c>
     </row>
@@ -42822,7 +42822,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-hard-challenge-298.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q298-logistics-tracker-responsive-panel-responsive-design-hard-challenge-298.html</t>
         </is>
       </c>
     </row>
@@ -42869,7 +42869,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q299-tourism-board-responsive-story-responsive-design-hard-challenge-299.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q299-tourism-board-responsive-story-responsive-design-hard-challenge-299.html</t>
         </is>
       </c>
     </row>
@@ -42916,7 +42916,7 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Nithya-sri-14/Frontend-Development-/main/expected-pictures/hard/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-hard-challenge-300.svg</t>
+          <t>https://raw.githack.com/Nithya-sri-14/Frontend-Development-/main/solutions/hard/responsive-design/q300-hackathon-hub-adaptive-framework-responsive-design-hard-challenge-300.html</t>
         </is>
       </c>
     </row>
